--- a/engineering/Osiris_PDB_REV1.1_XT60_Procurement_PnP.xlsx
+++ b/engineering/Osiris_PDB_REV1.1_XT60_Procurement_PnP.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement" sheetId="1" r:id="Radb0e0e8fb314376"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="2" r:id="R4b6248b0cdcc4465"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement" sheetId="1" r:id="R9e21bc6bba3c4cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="2" r:id="R84b1294069aa4d2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -468,9 +468,6 @@
     <x:t xml:space="preserve">1U0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">C2012X7R1H105K125AB</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">C3, C5, C8, C10</x:t>
   </x:si>
   <x:si>
@@ -525,9 +522,6 @@
     <x:t xml:space="preserve">100n 50V X7R</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">C0805C104K5RACTU</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">D1, D4</x:t>
   </x:si>
   <x:si>
@@ -663,18 +657,12 @@
     <x:t xml:space="preserve">2M0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-072ML</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R4</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">22k</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-0722KL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R5</x:t>
   </x:si>
   <x:si>
@@ -693,36 +681,24 @@
     <x:t xml:space="preserve">680k</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-07680KL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R7</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">200k</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-07200KL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R8, R9</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">10</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-0710RL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R10</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">4k7</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-074K7L</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R11</x:t>
   </x:si>
   <x:si>
@@ -738,9 +714,6 @@
     <x:t xml:space="preserve">1k0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-071KL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R13</x:t>
   </x:si>
   <x:si>
@@ -765,9 +738,6 @@
     <x:t xml:space="preserve">10k</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">RC0805FR-0710KL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">R19</x:t>
   </x:si>
   <x:si>
@@ -793,12 +763,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">100</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Yageo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RC0805FR-07100RL</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">U1</x:t>
@@ -871,7 +835,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="16">
+  <x:numFmts count="18">
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
     <x:numFmt numFmtId="166" formatCode="[$-409]General"/>
@@ -888,8 +852,10 @@
     <x:numFmt numFmtId="207" formatCode="0.000000"/>
     <x:numFmt numFmtId="208" formatCode="0.00000"/>
     <x:numFmt numFmtId="209" formatCode="0.0%"/>
+    <x:numFmt numFmtId="210" formatCode="0"/>
+    <x:numFmt numFmtId="211" formatCode="mm/dd/yy"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="30">
     <x:font>
       <x:sz val="10"/>
       <x:name val="Arial"/>
@@ -1017,8 +983,35 @@
       <x:color rgb="FF9C5700"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF252525"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF252525"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF666666"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF252525"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF555555"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1110,6 +1103,31 @@
         <x:fgColor rgb="FFA45A22"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F1F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F7F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFEFEF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border diagonalUp="0" diagonalDown="0"/>
@@ -1172,7 +1190,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="193">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="0" applyBorder="0" applyAlignment="0">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -1460,6 +1478,297 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="24" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="7" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="169" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="169" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="25" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="26" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="27" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="25" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="28" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="28" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="28" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="169" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="25" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="29" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="29" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="29" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="29" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="25" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="25" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="28" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="28" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="28" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="25" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="8">
@@ -1682,3555 +1991,3786 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.800000190734863"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.149999618530273" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="29.18000030517578" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="23.139999389648438" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="37.220001220703125" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.079999923706055" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.069999694824219" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.079999923706055" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.100000381469727" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="29" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
     <x:col min="9" max="10" width="18.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="11" max="12" width="22.139999389648438" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="35.220001220703125" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="15.09000015258789" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
     <x:col min="15" max="1024" width="8.720000267028809" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="21" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="21" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="21" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="21" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="65" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="28" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="65" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="11" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="13" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="37" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="24" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="13" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="60" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="2" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="2" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="27" hidden="0" customHeight="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="146" t="str">
         <x:v>Osiris PDB REV1.1 XT60 — Procurement and PnP</x:v>
       </x:c>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-      <x:c r="I1" s="1"/>
-      <x:c r="J1" s="1"/>
-      <x:c r="K1" s="1"/>
-      <x:c r="L1" s="1"/>
-      <x:c r="M1" s="1"/>
-      <x:c r="N1" s="1"/>
-    </x:row>
-    <x:row r="2" ht="24" hidden="0" customHeight="1">
-      <x:c r="A2" s="2" t="s">
+      <x:c r="B1" s="146"/>
+      <x:c r="C1" s="146"/>
+      <x:c r="D1" s="146"/>
+      <x:c r="E1" s="146"/>
+      <x:c r="F1" s="146"/>
+      <x:c r="G1" s="146"/>
+      <x:c r="H1" s="146"/>
+      <x:c r="I1" s="146"/>
+      <x:c r="J1" s="146"/>
+      <x:c r="K1" s="146"/>
+      <x:c r="L1" s="146"/>
+      <x:c r="M1" s="146"/>
+      <x:c r="N1" s="146"/>
+      <x:c r="O1" s="142"/>
+      <x:c r="P1" s="142"/>
+      <x:c r="Q1" s="142"/>
+      <x:c r="R1" s="142"/>
+      <x:c r="S1" s="142"/>
+      <x:c r="T1" s="142"/>
+      <x:c r="U1" s="142"/>
+      <x:c r="V1" s="142"/>
+      <x:c r="W1" s="142"/>
+      <x:c r="X1" s="142"/>
+      <x:c r="Y1" s="142"/>
+    </x:row>
+    <x:row r="2" ht="23" hidden="0" customHeight="1">
+      <x:c r="A2" s="147" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="2"/>
-      <x:c r="E2" s="2"/>
-      <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-      <x:c r="H2" s="2"/>
-      <x:c r="I2" s="2"/>
-      <x:c r="J2" s="2"/>
-      <x:c r="K2" s="2"/>
-      <x:c r="L2" s="2"/>
-      <x:c r="M2" s="2"/>
-      <x:c r="N2" s="2"/>
-      <x:c r="P2" s="26" t="str">
+      <x:c r="B2" s="147"/>
+      <x:c r="C2" s="147"/>
+      <x:c r="D2" s="147"/>
+      <x:c r="E2" s="147"/>
+      <x:c r="F2" s="147"/>
+      <x:c r="G2" s="147"/>
+      <x:c r="H2" s="147"/>
+      <x:c r="I2" s="147"/>
+      <x:c r="J2" s="147"/>
+      <x:c r="K2" s="147"/>
+      <x:c r="L2" s="147"/>
+      <x:c r="M2" s="147"/>
+      <x:c r="N2" s="147"/>
+      <x:c r="O2" s="142"/>
+      <x:c r="P2" s="182" t="str">
         <x:v>PnP purchasing guidance — October 7, 2026</x:v>
       </x:c>
-      <x:c r="Q2" s="26"/>
-      <x:c r="R2" s="26"/>
-      <x:c r="S2" s="26"/>
-      <x:c r="T2" s="26"/>
-      <x:c r="U2" s="26"/>
-    </x:row>
-    <x:row r="3" ht="24" hidden="0" customHeight="1">
-      <x:c r="A3" s="3"/>
-      <x:c r="B3" s="3"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="3"/>
-      <x:c r="F3" s="3"/>
-      <x:c r="G3" s="3"/>
-      <x:c r="H3" s="3"/>
-      <x:c r="I3" s="3"/>
-      <x:c r="J3" s="3"/>
-      <x:c r="K3" s="3"/>
-      <x:c r="L3" s="3"/>
-      <x:c r="M3" s="3"/>
-      <x:c r="N3" s="3"/>
-      <x:c r="P3" s="26" t="str">
+      <x:c r="Q2" s="182"/>
+      <x:c r="R2" s="182"/>
+      <x:c r="S2" s="182"/>
+      <x:c r="T2" s="182"/>
+      <x:c r="U2" s="182"/>
+      <x:c r="V2" s="142"/>
+      <x:c r="W2" s="142"/>
+      <x:c r="X2" s="142"/>
+      <x:c r="Y2" s="142"/>
+    </x:row>
+    <x:row r="3" ht="23" hidden="0" customHeight="1">
+      <x:c r="A3" s="124"/>
+      <x:c r="B3" s="124"/>
+      <x:c r="C3" s="124"/>
+      <x:c r="D3" s="124"/>
+      <x:c r="E3" s="124"/>
+      <x:c r="F3" s="124"/>
+      <x:c r="G3" s="124"/>
+      <x:c r="H3" s="124"/>
+      <x:c r="I3" s="124"/>
+      <x:c r="J3" s="124"/>
+      <x:c r="K3" s="124"/>
+      <x:c r="L3" s="124"/>
+      <x:c r="M3" s="124"/>
+      <x:c r="N3" s="124"/>
+      <x:c r="O3" s="142"/>
+      <x:c r="P3" s="182" t="str">
         <x:v>Passives: MAX(100, 10 × required qty). All other parts: +20%, rounded up.</x:v>
       </x:c>
-      <x:c r="Q3" s="26"/>
-      <x:c r="R3" s="26"/>
-      <x:c r="S3" s="26"/>
-      <x:c r="T3" s="26"/>
-      <x:c r="U3" s="26"/>
-    </x:row>
-    <x:row r="4" ht="24" hidden="0" customHeight="1">
-      <x:c r="A4" s="1" t="s">
+      <x:c r="Q3" s="182"/>
+      <x:c r="R3" s="182"/>
+      <x:c r="S3" s="182"/>
+      <x:c r="T3" s="182"/>
+      <x:c r="U3" s="182"/>
+      <x:c r="V3" s="142"/>
+      <x:c r="W3" s="142"/>
+      <x:c r="X3" s="142"/>
+      <x:c r="Y3" s="142"/>
+    </x:row>
+    <x:row r="4" ht="23" hidden="0" customHeight="1">
+      <x:c r="A4" s="152" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="n">
+      <x:c r="B4" s="180" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="C4" s="152"/>
+      <x:c r="D4" s="152" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="5" t="n">
+      <x:c r="E4" s="153" t="n">
         <x:f aca="0">SUM(I9:I50)</x:f>
-        <x:v>52.25699999999999</x:v>
-      </x:c>
-      <x:c r="F4" s="1"/>
-      <x:c r="G4" s="1" t="s">
+        <x:v>51.9389</x:v>
+      </x:c>
+      <x:c r="F4" s="152"/>
+      <x:c r="G4" s="152" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H4" s="5" t="n">
+      <x:c r="H4" s="153" t="n">
         <x:f aca="0">SUM(J9:J50)</x:f>
-        <x:v>261.28499999999997</x:v>
-      </x:c>
-      <x:c r="I4" s="1"/>
-      <x:c r="J4" s="1"/>
-      <x:c r="K4" s="1" t="s">
+        <x:v>259.6945</x:v>
+      </x:c>
+      <x:c r="I4" s="152"/>
+      <x:c r="J4" s="152"/>
+      <x:c r="K4" s="152" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L4" s="1" t="n">
+      <x:c r="L4" s="180" t="n">
         <x:f aca="0">COUNTIFS(M9:M50,"Short stock")</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="M4" s="1" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M4" s="152" t="str">
         <x:v>Unconfirmed stock</x:v>
       </x:c>
-      <x:c r="N4" s="1" t="n">
+      <x:c r="N4" s="180" t="n">
         <x:f>COUNTBLANK(N9:N50)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P4" s="26" t="str">
+      <x:c r="O4" s="142"/>
+      <x:c r="P4" s="182" t="str">
         <x:v>Full reels preferred. Use Digi-Reel/equivalent extenders for small tape orders.</x:v>
       </x:c>
-      <x:c r="Q4" s="26"/>
-      <x:c r="R4" s="26"/>
-      <x:c r="S4" s="26"/>
-      <x:c r="T4" s="26"/>
-      <x:c r="U4" s="26"/>
-    </x:row>
-    <x:row r="5" ht="24" hidden="0" customHeight="1">
-      <x:c r="A5" s="1"/>
-      <x:c r="B5" s="1"/>
-      <x:c r="C5" s="1"/>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
-      <x:c r="F5" s="1"/>
-      <x:c r="G5" s="1"/>
-      <x:c r="H5" s="1"/>
-      <x:c r="I5" s="1"/>
-      <x:c r="J5" s="1"/>
-      <x:c r="K5" s="1"/>
-      <x:c r="L5" s="1"/>
-      <x:c r="M5" s="1"/>
-      <x:c r="N5" s="1"/>
-      <x:c r="P5" s="26" t="str">
+      <x:c r="Q4" s="182"/>
+      <x:c r="R4" s="182"/>
+      <x:c r="S4" s="182"/>
+      <x:c r="T4" s="182"/>
+      <x:c r="U4" s="182"/>
+      <x:c r="V4" s="142"/>
+      <x:c r="W4" s="142"/>
+      <x:c r="X4" s="142"/>
+      <x:c r="Y4" s="142"/>
+    </x:row>
+    <x:row r="5" ht="23" hidden="0" customHeight="1">
+      <x:c r="A5" s="122"/>
+      <x:c r="B5" s="122"/>
+      <x:c r="C5" s="122"/>
+      <x:c r="D5" s="122"/>
+      <x:c r="E5" s="122"/>
+      <x:c r="F5" s="122"/>
+      <x:c r="G5" s="122"/>
+      <x:c r="H5" s="122"/>
+      <x:c r="I5" s="122"/>
+      <x:c r="J5" s="122"/>
+      <x:c r="K5" s="122"/>
+      <x:c r="L5" s="122"/>
+      <x:c r="M5" s="122"/>
+      <x:c r="N5" s="122"/>
+      <x:c r="O5" s="142"/>
+      <x:c r="P5" s="182" t="str">
         <x:v>Yellow override: round up for reel/MOQ. Recheck stock and prices at checkout.</x:v>
       </x:c>
-      <x:c r="Q5" s="26"/>
-      <x:c r="R5" s="26"/>
-      <x:c r="S5" s="26"/>
-      <x:c r="T5" s="26"/>
-      <x:c r="U5" s="26"/>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str">
+      <x:c r="Q5" s="182"/>
+      <x:c r="R5" s="182"/>
+      <x:c r="S5" s="182"/>
+      <x:c r="T5" s="182"/>
+      <x:c r="U5" s="182"/>
+      <x:c r="V5" s="142"/>
+      <x:c r="W5" s="142"/>
+      <x:c r="X5" s="142"/>
+      <x:c r="Y5" s="142"/>
+    </x:row>
+    <x:row r="6" ht="25" hidden="0" customHeight="1">
+      <x:c r="A6" s="184" t="str">
         <x:v>USD. Prices remain October 5, 2026 estimates. Stock and links checked October 8, 2026. PCB fabrication, assembly, freight, taxes, tariffs and reel fees excluded.</x:v>
       </x:c>
-      <x:c r="B6" s="6"/>
-      <x:c r="C6" s="6"/>
-      <x:c r="D6" s="6"/>
-      <x:c r="E6" s="6"/>
-      <x:c r="F6" s="6"/>
-      <x:c r="G6" s="6"/>
-      <x:c r="H6" s="6"/>
-      <x:c r="I6" s="6"/>
-      <x:c r="J6" s="6"/>
-      <x:c r="K6" s="6"/>
-      <x:c r="L6" s="6"/>
-      <x:c r="M6" s="6"/>
-      <x:c r="N6" s="6"/>
-      <x:c r="P6" s="26" t="str">
+      <x:c r="B6" s="184"/>
+      <x:c r="C6" s="184"/>
+      <x:c r="D6" s="184"/>
+      <x:c r="E6" s="184"/>
+      <x:c r="F6" s="184"/>
+      <x:c r="G6" s="184"/>
+      <x:c r="H6" s="184"/>
+      <x:c r="I6" s="184"/>
+      <x:c r="J6" s="184"/>
+      <x:c r="K6" s="184"/>
+      <x:c r="L6" s="184"/>
+      <x:c r="M6" s="184"/>
+      <x:c r="N6" s="184"/>
+      <x:c r="O6" s="142"/>
+      <x:c r="P6" s="182" t="str">
         <x:v>Stencil frame: 370 × 470 mm. Ryan to review thickness; Dr. Morton to confirm.</x:v>
       </x:c>
-      <x:c r="Q6" s="26"/>
-      <x:c r="R6" s="26"/>
-      <x:c r="S6" s="26"/>
-      <x:c r="T6" s="26"/>
-      <x:c r="U6" s="26"/>
-    </x:row>
-    <x:row r="7" ht="24" hidden="0" customHeight="1">
-      <x:c r="A7" s="6" t="str">
+      <x:c r="Q6" s="182"/>
+      <x:c r="R6" s="182"/>
+      <x:c r="S6" s="182"/>
+      <x:c r="T6" s="182"/>
+      <x:c r="U6" s="182"/>
+      <x:c r="V6" s="142"/>
+      <x:c r="W6" s="142"/>
+      <x:c r="X6" s="142"/>
+      <x:c r="Y6" s="142"/>
+    </x:row>
+    <x:row r="7" ht="25" hidden="0" customHeight="1">
+      <x:c r="A7" s="184" t="str">
         <x:v>REV1.1 protection correction: D5 SMBJ18CA; C17 330 uF / 50 V. Two replacement parts need fresh quotes; totals exclude unquoted parts. See Calculations and PROTECTION_FIX_STATUS.md.</x:v>
       </x:c>
-      <x:c r="B7" s="6"/>
-      <x:c r="C7" s="6"/>
-      <x:c r="D7" s="6"/>
-      <x:c r="E7" s="6"/>
-      <x:c r="F7" s="6"/>
-      <x:c r="G7" s="6"/>
-      <x:c r="H7" s="6"/>
-      <x:c r="I7" s="6"/>
-      <x:c r="J7" s="6"/>
-      <x:c r="K7" s="6"/>
-      <x:c r="L7" s="6"/>
-      <x:c r="M7" s="6"/>
-      <x:c r="N7" s="6"/>
-      <x:c r="P7" s="26" t="str">
+      <x:c r="B7" s="184"/>
+      <x:c r="C7" s="184"/>
+      <x:c r="D7" s="184"/>
+      <x:c r="E7" s="184"/>
+      <x:c r="F7" s="184"/>
+      <x:c r="G7" s="184"/>
+      <x:c r="H7" s="184"/>
+      <x:c r="I7" s="184"/>
+      <x:c r="J7" s="184"/>
+      <x:c r="K7" s="184"/>
+      <x:c r="L7" s="184"/>
+      <x:c r="M7" s="184"/>
+      <x:c r="N7" s="184"/>
+      <x:c r="O7" s="142"/>
+      <x:c r="P7" s="182" t="str">
         <x:v>Paste: consult Dr. Morton. PnP model/feeders: awaiting Dr. Cao.</x:v>
       </x:c>
-      <x:c r="Q7" s="26"/>
-      <x:c r="R7" s="26"/>
-      <x:c r="S7" s="26"/>
-      <x:c r="T7" s="26"/>
-      <x:c r="U7" s="26"/>
-    </x:row>
-    <x:row r="8" ht="42" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="s">
+      <x:c r="Q7" s="182"/>
+      <x:c r="R7" s="182"/>
+      <x:c r="S7" s="182"/>
+      <x:c r="T7" s="182"/>
+      <x:c r="U7" s="182"/>
+      <x:c r="V7" s="142"/>
+      <x:c r="W7" s="142"/>
+      <x:c r="X7" s="142"/>
+      <x:c r="Y7" s="142"/>
+    </x:row>
+    <x:row r="8" ht="40" hidden="0" customHeight="1">
+      <x:c r="A8" s="160" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="s">
+      <x:c r="B8" s="161" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="s">
+      <x:c r="C8" s="161" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="s">
+      <x:c r="D8" s="161" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="s">
+      <x:c r="E8" s="161" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="s">
+      <x:c r="F8" s="161" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="s">
+      <x:c r="G8" s="161" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H8" s="8" t="s">
+      <x:c r="H8" s="161" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="s">
+      <x:c r="I8" s="161" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J8" s="8" t="s">
+      <x:c r="J8" s="161" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K8" s="8" t="s">
+      <x:c r="K8" s="161" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L8" s="8" t="s">
+      <x:c r="L8" s="161" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="M8" s="8" t="str">
+      <x:c r="M8" s="161" t="str">
         <x:v>Stock vs order qty</x:v>
       </x:c>
-      <x:c r="N8" s="9" t="str">
+      <x:c r="N8" s="162" t="str">
         <x:v>Reported stock</x:v>
       </x:c>
-      <x:c r="P8" s="25" t="str">
+      <x:c r="O8" s="142"/>
+      <x:c r="P8" s="166" t="str">
         <x:v>Minimum buy qty</x:v>
       </x:c>
-      <x:c r="Q8" s="25" t="str">
+      <x:c r="Q8" s="166" t="str">
         <x:v>Order qty override</x:v>
       </x:c>
-      <x:c r="R8" s="25" t="str">
+      <x:c r="R8" s="166" t="str">
         <x:v>Order qty</x:v>
       </x:c>
-      <x:c r="S8" s="25" t="str">
+      <x:c r="S8" s="166" t="str">
         <x:v>Order cost (USD)</x:v>
       </x:c>
-      <x:c r="T8" s="25" t="str">
+      <x:c r="T8" s="166" t="str">
         <x:v>Quantity rule</x:v>
       </x:c>
-      <x:c r="U8" s="25" t="str">
+      <x:c r="U8" s="166" t="str">
         <x:v>Buyer comments</x:v>
       </x:c>
-      <x:c r="W8" s="37" t="str">
+      <x:c r="V8" s="142"/>
+      <x:c r="W8" s="166" t="str">
         <x:v>Purchase link check</x:v>
       </x:c>
-      <x:c r="X8" s="37" t="str">
+      <x:c r="X8" s="166" t="str">
         <x:v>Stock checked</x:v>
       </x:c>
-      <x:c r="Y8" s="37" t="str">
+      <x:c r="Y8" s="166" t="str">
         <x:v>Stock details</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" hidden="0" customHeight="1">
-      <x:c r="A9" s="10" t="s">
+    <x:row r="9" ht="28" hidden="0" customHeight="1">
+      <x:c r="A9" s="130" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B9" s="10" t="s">
+      <x:c r="B9" s="130" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C9" s="10" t="s">
+      <x:c r="C9" s="130" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="10" t="s">
+      <x:c r="D9" s="130" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="E9" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
+      <x:c r="F9" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="n">
+      <x:c r="G9" s="131" t="n">
         <x:f aca="0">F9*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H9" s="12" t="n">
+      <x:c r="H9" s="132" t="n">
         <x:f aca="0">IF(R9&gt;=500,0.09666,IF(R9&gt;=100,0.1236,IF(R9&gt;=50,0.1396,IF(R9&gt;=10,0.192,0.33))))</x:f>
         <x:v>0.1236</x:v>
       </x:c>
-      <x:c r="I9" s="13" t="n">
+      <x:c r="I9" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H9),F9*H9,"")</x:f>
         <x:v>0.1236</x:v>
       </x:c>
-      <x:c r="J9" s="13" t="n">
+      <x:c r="J9" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H9),G9*H9,"")</x:f>
         <x:v>0.618</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="s">
+      <x:c r="K9" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L9" s="1" t="s">
+      <x:c r="L9" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M9" s="1" t="str">
+      <x:c r="M9" s="130" t="str">
         <x:f>IF(ISNUMBER(N9),IF(N9&lt;R9,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N9" s="39" t="n">
+      <x:c r="N9" s="131" t="n">
         <x:v>32275</x:v>
       </x:c>
-      <x:c r="P9" s="29" t="n">
+      <x:c r="O9" s="167"/>
+      <x:c r="P9" s="131" t="n">
         <x:f>IF(G9=0,0,MAX(100,10*G9))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q9" s="30"/>
-      <x:c r="R9" s="29" t="n">
+      <x:c r="Q9" s="178"/>
+      <x:c r="R9" s="131" t="n">
         <x:f>IF(Q9="",P9,MAX(P9,Q9))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S9" s="31" t="n">
+      <x:c r="S9" s="168" t="n">
         <x:f>IF(ISNUMBER(H9),R9*H9,"")</x:f>
         <x:v>12.36</x:v>
       </x:c>
-      <x:c r="T9" s="26" t="str">
+      <x:c r="T9" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U9" s="27" t="str">
+      <x:c r="U9" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W9" s="27" t="str">
+      <x:c r="V9" s="142"/>
+      <x:c r="W9" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X9" s="38" t="d">
+      <x:c r="X9" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y9" s="27" t="str">
+      <x:c r="Y9" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" hidden="0" customHeight="1">
-      <x:c r="A10" s="15" t="s">
+    <x:row r="10" ht="28" hidden="0" customHeight="1">
+      <x:c r="A10" s="179" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="179" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="n">
+      <x:c r="C10" s="179" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D10" s="179" t="str">
+        <x:v>CC0805KKX7R9BB105</x:v>
+      </x:c>
+      <x:c r="E10" s="169" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F10" s="170" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="n">
+      <x:c r="G10" s="170" t="n">
         <x:f aca="0">F10*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H10" s="18" t="n">
-        <x:f aca="0">IF(R10&gt;=100,0.0892,IF(R10&gt;=50,0.1014,IF(R10&gt;=10,0.141,0.24)))</x:f>
-        <x:v>0.0892</x:v>
-      </x:c>
-      <x:c r="I10" s="19" t="n">
+      <x:c r="H10" s="171" t="n">
+        <x:f aca="0">IF(R10&gt;=21000,0.0194,IF(R10&gt;=9000,0.02,IF(R10&gt;=3000,0.0209,IF(R10&gt;=600,0.0232,IF(R10&gt;=200,0.0262,0.033)))))</x:f>
+        <x:v>0.033</x:v>
+      </x:c>
+      <x:c r="I10" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H10),F10*H10,"")</x:f>
-        <x:v>0.1784</x:v>
-      </x:c>
-      <x:c r="J10" s="19" t="n">
+        <x:v>0.066</x:v>
+      </x:c>
+      <x:c r="J10" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H10),G10*H10,"")</x:f>
-        <x:v>0.892</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L10" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="str">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="K10" s="169" t="str">
+        <x:v>LCSC C91185</x:v>
+      </x:c>
+      <x:c r="L10" s="169" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M10" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N10),IF(N10&lt;R10,"Short stock","Available"),"Stock unconfirmed")</x:f>
-        <x:v>Short stock</x:v>
-      </x:c>
-      <x:c r="N10" s="40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="29" t="n">
-        <x:f>IF(G10=0,0,MAX(100,10*G10))</x:f>
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="N10" s="170" t="n">
+        <x:v>767960</x:v>
+      </x:c>
+      <x:c r="O10" s="167"/>
+      <x:c r="P10" s="170" t="n">
+        <x:f>IF(G10=0,0,CEILING(MAX(100,10*G10),20))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q10" s="30"/>
-      <x:c r="R10" s="29" t="n">
-        <x:f>IF(Q10="",P10,MAX(P10,Q10))</x:f>
+      <x:c r="Q10" s="178"/>
+      <x:c r="R10" s="170" t="n">
+        <x:f>IF(Q10="",P10,CEILING(MAX(P10,Q10),20))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S10" s="31" t="n">
+      <x:c r="S10" s="177" t="n">
         <x:f>IF(ISNUMBER(H10),R10*H10,"")</x:f>
-        <x:v>8.92</x:v>
-      </x:c>
-      <x:c r="T10" s="26" t="str">
+        <x:v>3.3000000000000003</x:v>
+      </x:c>
+      <x:c r="T10" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U10" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W10" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X10" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y10" s="27" t="str">
-        <x:v>Supplier expects 2,000 on Dec 1, 2026. Expected arrivals are estimates.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="27" hidden="0" customHeight="1">
-      <x:c r="A11" s="10" t="s">
+      <x:c r="U10" s="175" t="str">
+        <x:v>Same value/package. 50 V, X7R, ±10%. C91185. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V10" s="142"/>
+      <x:c r="W10" s="175" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X10" s="191" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y10" s="175" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C91185.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28" hidden="0" customHeight="1">
+      <x:c r="A11" s="130" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B11" s="130" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B11" s="10" t="s">
+      <x:c r="C11" s="130" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C11" s="10" t="s">
+      <x:c r="D11" s="130" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D11" s="10" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="E11" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="n">
+      <x:c r="F11" s="131" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="n">
+      <x:c r="G11" s="131" t="n">
         <x:f aca="0">F11*$B$4</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="n">
+      <x:c r="H11" s="132" t="n">
         <x:f aca="0">IF(R11&gt;=500,0.03184,IF(R11&gt;=100,0.0434,IF(R11&gt;=50,0.0504,IF(R11&gt;=10,0.073,0.13))))</x:f>
         <x:v>0.0434</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="n">
+      <x:c r="I11" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H11),F11*H11,"")</x:f>
         <x:v>0.1736</x:v>
       </x:c>
-      <x:c r="J11" s="13" t="n">
+      <x:c r="J11" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H11),G11*H11,"")</x:f>
         <x:v>0.868</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="s">
+      <x:c r="K11" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L11" s="1" t="s">
+      <x:c r="L11" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M11" s="1" t="str">
+      <x:c r="M11" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N11),IF(N11&lt;R11,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N11" s="39" t="n">
+      <x:c r="N11" s="131" t="n">
         <x:v>6710508</x:v>
       </x:c>
-      <x:c r="P11" s="29" t="n">
+      <x:c r="O11" s="167"/>
+      <x:c r="P11" s="131" t="n">
         <x:f>IF(G11=0,0,MAX(100,10*G11))</x:f>
         <x:v>200</x:v>
       </x:c>
-      <x:c r="Q11" s="30"/>
-      <x:c r="R11" s="29" t="n">
+      <x:c r="Q11" s="178"/>
+      <x:c r="R11" s="131" t="n">
         <x:f>IF(Q11="",P11,MAX(P11,Q11))</x:f>
         <x:v>200</x:v>
       </x:c>
-      <x:c r="S11" s="31" t="n">
+      <x:c r="S11" s="168" t="n">
         <x:f>IF(ISNUMBER(H11),R11*H11,"")</x:f>
         <x:v>8.68</x:v>
       </x:c>
-      <x:c r="T11" s="26" t="str">
+      <x:c r="T11" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U11" s="27" t="str">
+      <x:c r="U11" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W11" s="27" t="str">
+      <x:c r="V11" s="142"/>
+      <x:c r="W11" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X11" s="38" t="d">
+      <x:c r="X11" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y11" s="27" t="str">
+      <x:c r="Y11" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" hidden="0" customHeight="1">
-      <x:c r="A12" s="15" t="s">
+    <x:row r="12" ht="28" hidden="0" customHeight="1">
+      <x:c r="A12" s="179" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B12" s="179" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B12" s="15" t="s">
+      <x:c r="C12" s="179" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D12" s="179" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E12" s="16" t="s">
+      <x:c r="E12" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="n">
+      <x:c r="F12" s="170" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="n">
+      <x:c r="G12" s="170" t="n">
         <x:f aca="0">F12*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H12" s="18" t="n">
+      <x:c r="H12" s="171" t="n">
         <x:f aca="0">IF(R12&gt;=500,0.36358,IF(R12&gt;=100,0.4366,IF(R12&gt;=50,0.4798,IF(R12&gt;=10,0.62,0.98))))</x:f>
         <x:v>0.4366</x:v>
       </x:c>
-      <x:c r="I12" s="19" t="n">
+      <x:c r="I12" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H12),F12*H12,"")</x:f>
         <x:v>0.8732</x:v>
       </x:c>
-      <x:c r="J12" s="19" t="n">
+      <x:c r="J12" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H12),G12*H12,"")</x:f>
         <x:v>4.366</x:v>
       </x:c>
-      <x:c r="K12" s="20" t="s">
+      <x:c r="K12" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L12" s="16" t="s">
+      <x:c r="L12" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="str">
+      <x:c r="M12" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N12),IF(N12&lt;R12,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Short stock</x:v>
       </x:c>
-      <x:c r="N12" s="40" t="n">
+      <x:c r="N12" s="170" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P12" s="29" t="n">
+      <x:c r="O12" s="167"/>
+      <x:c r="P12" s="170" t="n">
         <x:f>IF(G12=0,0,MAX(100,10*G12))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q12" s="30"/>
-      <x:c r="R12" s="29" t="n">
+      <x:c r="Q12" s="178"/>
+      <x:c r="R12" s="170" t="n">
         <x:f>IF(Q12="",P12,MAX(P12,Q12))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S12" s="31" t="n">
+      <x:c r="S12" s="177" t="n">
         <x:f>IF(ISNUMBER(H12),R12*H12,"")</x:f>
         <x:v>43.66</x:v>
       </x:c>
-      <x:c r="T12" s="26" t="str">
+      <x:c r="T12" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U12" s="27" t="str">
+      <x:c r="U12" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W12" s="27" t="str">
+      <x:c r="V12" s="142"/>
+      <x:c r="W12" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X12" s="38" t="d">
+      <x:c r="X12" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y12" s="27" t="str">
+      <x:c r="Y12" s="175" t="str">
         <x:v>Supplier expects 2,000 on Dec 14, 2026. Expected arrivals are estimates.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" hidden="0" customHeight="1">
-      <x:c r="A13" s="10" t="s">
+    <x:row r="13" ht="28" hidden="0" customHeight="1">
+      <x:c r="A13" s="130" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B13" s="130" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="130" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D13" s="130" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B13" s="10" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="10" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D13" s="10" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="E13" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="n">
+      <x:c r="F13" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="n">
+      <x:c r="G13" s="131" t="n">
         <x:f aca="0">F13*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H13" s="12" t="n">
+      <x:c r="H13" s="132" t="n">
         <x:f aca="0">IF(R13&gt;=100,0.1218,IF(R13&gt;=50,0.1376,IF(R13&gt;=10,0.189,0.32)))</x:f>
         <x:v>0.1218</x:v>
       </x:c>
-      <x:c r="I13" s="13" t="n">
+      <x:c r="I13" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H13),F13*H13,"")</x:f>
         <x:v>0.1218</x:v>
       </x:c>
-      <x:c r="J13" s="13" t="n">
+      <x:c r="J13" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H13),G13*H13,"")</x:f>
         <x:v>0.609</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="s">
+      <x:c r="K13" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L13" s="1" t="s">
+      <x:c r="L13" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M13" s="1" t="str">
+      <x:c r="M13" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N13),IF(N13&lt;R13,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Short stock</x:v>
       </x:c>
-      <x:c r="N13" s="39" t="n">
+      <x:c r="N13" s="131" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P13" s="29" t="n">
+      <x:c r="O13" s="167"/>
+      <x:c r="P13" s="131" t="n">
         <x:f>IF(G13=0,0,MAX(100,10*G13))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q13" s="30"/>
-      <x:c r="R13" s="29" t="n">
+      <x:c r="Q13" s="178"/>
+      <x:c r="R13" s="131" t="n">
         <x:f>IF(Q13="",P13,MAX(P13,Q13))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S13" s="31" t="n">
+      <x:c r="S13" s="168" t="n">
         <x:f>IF(ISNUMBER(H13),R13*H13,"")</x:f>
         <x:v>12.18</x:v>
       </x:c>
-      <x:c r="T13" s="26" t="str">
+      <x:c r="T13" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U13" s="27" t="str">
+      <x:c r="U13" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W13" s="27" t="str">
+      <x:c r="V13" s="142"/>
+      <x:c r="W13" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X13" s="38" t="d">
+      <x:c r="X13" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y13" s="27" t="str">
+      <x:c r="Y13" s="142" t="str">
         <x:v>Only 20 reported; order minimum is 100. Source more of the same MPN or approve a substitute.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" hidden="0" customHeight="1">
-      <x:c r="A14" s="15" t="s">
+    <x:row r="14" ht="28" hidden="0" customHeight="1">
+      <x:c r="A14" s="179" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B14" s="179" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="179" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D14" s="179" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B14" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
+      <x:c r="E14" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F14" s="17" t="n">
+      <x:c r="F14" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G14" s="17" t="n">
+      <x:c r="G14" s="170" t="n">
         <x:f aca="0">F14*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H14" s="18" t="n">
+      <x:c r="H14" s="171" t="n">
         <x:f aca="0">IF(R14&gt;=500,0.02634,IF(R14&gt;=100,0.0359,IF(R14&gt;=50,0.0416,IF(R14&gt;=10,0.06,0.11))))</x:f>
         <x:v>0.0359</x:v>
       </x:c>
-      <x:c r="I14" s="19" t="n">
+      <x:c r="I14" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H14),F14*H14,"")</x:f>
         <x:v>0.0359</x:v>
       </x:c>
-      <x:c r="J14" s="19" t="n">
+      <x:c r="J14" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H14),G14*H14,"")</x:f>
         <x:v>0.1795</x:v>
       </x:c>
-      <x:c r="K14" s="20" t="s">
+      <x:c r="K14" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L14" s="16" t="s">
+      <x:c r="L14" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="str">
+      <x:c r="M14" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N14),IF(N14&lt;R14,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Short stock</x:v>
       </x:c>
-      <x:c r="N14" s="40" t="n">
+      <x:c r="N14" s="170" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P14" s="29" t="n">
+      <x:c r="O14" s="167"/>
+      <x:c r="P14" s="170" t="n">
         <x:f>IF(G14=0,0,MAX(100,10*G14))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q14" s="30"/>
-      <x:c r="R14" s="29" t="n">
+      <x:c r="Q14" s="178"/>
+      <x:c r="R14" s="170" t="n">
         <x:f>IF(Q14="",P14,MAX(P14,Q14))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S14" s="31" t="n">
+      <x:c r="S14" s="177" t="n">
         <x:f>IF(ISNUMBER(H14),R14*H14,"")</x:f>
         <x:v>3.5900000000000003</x:v>
       </x:c>
-      <x:c r="T14" s="26" t="str">
+      <x:c r="T14" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U14" s="27" t="str">
+      <x:c r="U14" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W14" s="27" t="str">
+      <x:c r="V14" s="142"/>
+      <x:c r="W14" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X14" s="38" t="d">
+      <x:c r="X14" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y14" s="27" t="str">
+      <x:c r="Y14" s="175" t="str">
         <x:v>Supplier expects 4,000 on Oct 21, 2026. Expected arrivals are estimates.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" hidden="0" customHeight="1">
-      <x:c r="A15" s="10" t="s">
+    <x:row r="15" ht="34" hidden="0" customHeight="1">
+      <x:c r="A15" s="130" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B15" s="130" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B15" s="10" t="s">
+      <x:c r="C15" s="130" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D15" s="130" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C15" s="10" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="10" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
+      <x:c r="E15" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="n">
+      <x:c r="F15" s="131" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="n">
+      <x:c r="G15" s="131" t="n">
         <x:f aca="0">F15*$B$4</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="n">
+      <x:c r="H15" s="132" t="n">
         <x:f aca="0">IF(R15&gt;=500,0.29306,IF(R15&gt;=100,0.3543,IF(R15&gt;=50,0.3906,IF(R15&gt;=10,0.508,0.81))))</x:f>
         <x:v>0.3543</x:v>
       </x:c>
-      <x:c r="I15" s="13" t="n">
+      <x:c r="I15" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H15),F15*H15,"")</x:f>
         <x:v>2.1258</x:v>
       </x:c>
-      <x:c r="J15" s="13" t="n">
+      <x:c r="J15" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H15),G15*H15,"")</x:f>
         <x:v>10.629</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="s">
+      <x:c r="K15" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L15" s="1" t="s">
+      <x:c r="L15" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M15" s="1" t="str">
+      <x:c r="M15" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N15),IF(N15&lt;R15,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Short stock</x:v>
       </x:c>
-      <x:c r="N15" s="39" t="n">
+      <x:c r="N15" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P15" s="29" t="n">
+      <x:c r="O15" s="167"/>
+      <x:c r="P15" s="131" t="n">
         <x:f>IF(G15=0,0,MAX(100,10*G15))</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="Q15" s="30"/>
-      <x:c r="R15" s="29" t="n">
+      <x:c r="Q15" s="178"/>
+      <x:c r="R15" s="131" t="n">
         <x:f>IF(Q15="",P15,MAX(P15,Q15))</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="S15" s="31" t="n">
+      <x:c r="S15" s="168" t="n">
         <x:f>IF(ISNUMBER(H15),R15*H15,"")</x:f>
         <x:v>106.29</x:v>
       </x:c>
-      <x:c r="T15" s="26" t="str">
+      <x:c r="T15" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U15" s="27" t="str">
+      <x:c r="U15" s="142" t="str">
         <x:v>Confirm handling of this leaded capacitor with assembly team. Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W15" s="27" t="str">
+      <x:c r="V15" s="142"/>
+      <x:c r="W15" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X15" s="38" t="d">
+      <x:c r="X15" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y15" s="27" t="str">
+      <x:c r="Y15" s="142" t="str">
         <x:v>Only 1 reported; order minimum is 300. Source more of the same MPN or approve a substitute.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" hidden="0" customHeight="1">
-      <x:c r="A16" s="15" t="s">
+    <x:row r="16" ht="38" hidden="0" customHeight="1">
+      <x:c r="A16" s="179" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B16" s="179" t="str">
+        <x:v>330 uF / 50 V hybrid capacitor</x:v>
+      </x:c>
+      <x:c r="C16" s="179" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B16" s="15" t="str">
-        <x:v>330 uF / 50 V hybrid capacitor</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="D16" s="179" t="str">
         <x:v>EEHZL1H331P</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="s">
+      <x:c r="E16" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F16" s="17" t="n">
+      <x:c r="F16" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G16" s="17" t="n">
+      <x:c r="G16" s="170" t="n">
         <x:f aca="0">F16*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H16" s="18">
+      <x:c r="H16" s="171">
         <x:f aca="0"/>
       </x:c>
-      <x:c r="I16" s="19" t="str">
+      <x:c r="I16" s="172" t="str">
         <x:f aca="0">IF(ISNUMBER(H16),F16*H16,"")</x:f>
       </x:c>
-      <x:c r="J16" s="19" t="str">
+      <x:c r="J16" s="172" t="str">
         <x:f aca="0">IF(ISNUMBER(H16),G16*H16,"")</x:f>
       </x:c>
-      <x:c r="K16" s="20" t="str">
+      <x:c r="K16" s="169" t="str">
         <x:v>Updated part: quote required</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="str">
+      <x:c r="L16" s="169" t="str">
         <x:v>Unquoted replacement</x:v>
       </x:c>
-      <x:c r="M16" s="16" t="str">
+      <x:c r="M16" s="179" t="str">
         <x:f aca="0"/>
         <x:v>Stock unconfirmed</x:v>
       </x:c>
-      <x:c r="N16" s="40"/>
-      <x:c r="P16" s="29" t="n">
+      <x:c r="N16" s="170"/>
+      <x:c r="O16" s="167"/>
+      <x:c r="P16" s="170" t="n">
         <x:f>IF(G16=0,0,MAX(100,10*G16))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q16" s="30"/>
-      <x:c r="R16" s="29" t="n">
+      <x:c r="Q16" s="178"/>
+      <x:c r="R16" s="170" t="n">
         <x:f>IF(Q16="",P16,MAX(P16,Q16))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S16" s="31" t="str">
+      <x:c r="S16" s="177" t="str">
         <x:f>IF(ISNUMBER(H16),R16*H16,"")</x:f>
       </x:c>
-      <x:c r="T16" s="26" t="str">
+      <x:c r="T16" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U16" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W16" s="27" t="str">
+      <x:c r="U16" s="175" t="str">
+        <x:v>Retained: 330 µF, 50 V hybrid; 12 mΩ ESR and 5 A ripple at 125 °C. No verified direct replacement meeting all three requirements.</x:v>
+      </x:c>
+      <x:c r="V16" s="142"/>
+      <x:c r="W16" s="175" t="str">
         <x:v>Replacement; sourcing unverified</x:v>
       </x:c>
-      <x:c r="X16" s="38"/>
-      <x:c r="Y16" s="27" t="str">
-        <x:v>Previous part price/stock no longer applies. Source: https://industrial.panasonic.com/ww/products/pt/hybrid-aluminum/models/EEHZL1H331P</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="27" hidden="0" customHeight="1">
-      <x:c r="A17" s="10" t="s">
+      <x:c r="X16" s="176"/>
+      <x:c r="Y16" s="175" t="str">
+        <x:v>C17 reviewed 10/08/26. Ordinary electrolytic and 220 µF alternatives are not approved direct substitutions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28" hidden="0" customHeight="1">
+      <x:c r="A17" s="130" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B17" s="130" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B17" s="10" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C17" s="10" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D17" s="10" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="n">
+      <x:c r="C17" s="130" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D17" s="130" t="str">
+        <x:v>CC0805KRX7R9BB104</x:v>
+      </x:c>
+      <x:c r="E17" s="122" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F17" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="n">
+      <x:c r="G17" s="131" t="n">
         <x:f aca="0">F17*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="n">
-        <x:f aca="0">IF(R17&gt;=500,0.0454,IF(R17&gt;=100,0.0608,IF(R17&gt;=50,0.07,IF(R17&gt;=10,0.1,0.18))))</x:f>
-        <x:v>0.0608</x:v>
-      </x:c>
-      <x:c r="I17" s="13" t="n">
+      <x:c r="H17" s="132" t="n">
+        <x:f aca="0">IF(R17&gt;=20000,0.0087,IF(R17&gt;=8000,0.0092,IF(R17&gt;=4000,0.0098,IF(R17&gt;=600,0.0119,IF(R17&gt;=200,0.0141,0.0191)))))</x:f>
+        <x:v>0.0191</x:v>
+      </x:c>
+      <x:c r="I17" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H17),F17*H17,"")</x:f>
-        <x:v>0.0608</x:v>
-      </x:c>
-      <x:c r="J17" s="13" t="n">
+        <x:v>0.0191</x:v>
+      </x:c>
+      <x:c r="J17" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H17),G17*H17,"")</x:f>
-        <x:v>0.304</x:v>
-      </x:c>
-      <x:c r="K17" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L17" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M17" s="1" t="str">
+        <x:v>0.0955</x:v>
+      </x:c>
+      <x:c r="K17" s="122" t="str">
+        <x:v>LCSC C49678</x:v>
+      </x:c>
+      <x:c r="L17" s="122" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M17" s="130" t="str">
         <x:f>IF(ISNUMBER(N17),IF(N17&lt;R17,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N17" s="39" t="n">
-        <x:v>6375398</x:v>
-      </x:c>
-      <x:c r="P17" s="29" t="n">
-        <x:f>IF(G17=0,0,MAX(100,10*G17))</x:f>
+      <x:c r="N17" s="131" t="n">
+        <x:v>8362320</x:v>
+      </x:c>
+      <x:c r="O17" s="167"/>
+      <x:c r="P17" s="131" t="n">
+        <x:f>IF(G17=0,0,CEILING(MAX(100,10*G17),20))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q17" s="30"/>
-      <x:c r="R17" s="29" t="n">
-        <x:f>IF(Q17="",P17,MAX(P17,Q17))</x:f>
+      <x:c r="Q17" s="178"/>
+      <x:c r="R17" s="131" t="n">
+        <x:f>IF(Q17="",P17,CEILING(MAX(P17,Q17),20))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S17" s="31" t="n">
+      <x:c r="S17" s="168" t="n">
         <x:f>IF(ISNUMBER(H17),R17*H17,"")</x:f>
-        <x:v>6.08</x:v>
-      </x:c>
-      <x:c r="T17" s="26" t="str">
+        <x:v>1.91</x:v>
+      </x:c>
+      <x:c r="T17" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U17" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W17" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X17" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y17" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="27" hidden="0" customHeight="1">
-      <x:c r="A18" s="15" t="s">
+      <x:c r="U17" s="142" t="str">
+        <x:v>Same value/package. 50 V, X7R, ±10%. C49678. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V17" s="142"/>
+      <x:c r="W17" s="142" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X17" s="192" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y17" s="142" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C49678.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="28" hidden="0" customHeight="1">
+      <x:c r="A18" s="179" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B18" s="179" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C18" s="179" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B18" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
+      <x:c r="D18" s="179" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E18" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F18" s="17" t="n">
+      <x:c r="F18" s="170" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G18" s="17" t="n">
+      <x:c r="G18" s="170" t="n">
         <x:f aca="0">F18*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H18" s="18" t="n">
+      <x:c r="H18" s="171" t="n">
         <x:f aca="0">IF(R18&gt;=100,0.2431,IF(R18&gt;=50,0.2772,IF(R18&gt;=10,0.382,0.62)))</x:f>
         <x:v>0.382</x:v>
       </x:c>
-      <x:c r="I18" s="19" t="n">
+      <x:c r="I18" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H18),F18*H18,"")</x:f>
         <x:v>0.764</x:v>
       </x:c>
-      <x:c r="J18" s="19" t="n">
+      <x:c r="J18" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H18),G18*H18,"")</x:f>
         <x:v>3.8200000000000003</x:v>
       </x:c>
-      <x:c r="K18" s="20" t="s">
+      <x:c r="K18" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="s">
+      <x:c r="L18" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M18" s="16" t="str">
+      <x:c r="M18" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N18),IF(N18&lt;R18,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N18" s="40" t="n">
+      <x:c r="N18" s="170" t="n">
         <x:v>48573</x:v>
       </x:c>
-      <x:c r="P18" s="29" t="n">
+      <x:c r="O18" s="167"/>
+      <x:c r="P18" s="170" t="n">
         <x:f>ROUNDUP(G18*1.2,0)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="Q18" s="30"/>
-      <x:c r="R18" s="29" t="n">
+      <x:c r="Q18" s="178"/>
+      <x:c r="R18" s="170" t="n">
         <x:f>IF(Q18="",P18,MAX(P18,Q18))</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="S18" s="31" t="n">
+      <x:c r="S18" s="177" t="n">
         <x:f>IF(ISNUMBER(H18),R18*H18,"")</x:f>
         <x:v>4.584</x:v>
       </x:c>
-      <x:c r="T18" s="26" t="str">
+      <x:c r="T18" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U18" s="27" t="str">
+      <x:c r="U18" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W18" s="27" t="str">
+      <x:c r="V18" s="142"/>
+      <x:c r="W18" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X18" s="38" t="d">
+      <x:c r="X18" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y18" s="27" t="str">
+      <x:c r="Y18" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" hidden="0" customHeight="1">
-      <x:c r="A19" s="10" t="s">
+    <x:row r="19" ht="28" hidden="0" customHeight="1">
+      <x:c r="A19" s="130" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B19" s="130" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C19" s="130" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B19" s="10" t="s">
+      <x:c r="D19" s="130" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C19" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D19" s="10" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
+      <x:c r="E19" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="n">
+      <x:c r="F19" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="n">
+      <x:c r="G19" s="131" t="n">
         <x:f aca="0">F19*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H19" s="12" t="n">
+      <x:c r="H19" s="132" t="n">
         <x:f aca="0">IF(R19&gt;=500,0.48634,IF(R19&gt;=100,0.6225,IF(R19&gt;=50,0.7,IF(R19&gt;=10,0.94,1.49))))</x:f>
         <x:v>1.49</x:v>
       </x:c>
-      <x:c r="I19" s="13" t="n">
+      <x:c r="I19" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H19),F19*H19,"")</x:f>
         <x:v>1.49</x:v>
       </x:c>
-      <x:c r="J19" s="13" t="n">
+      <x:c r="J19" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H19),G19*H19,"")</x:f>
         <x:v>7.45</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="s">
+      <x:c r="K19" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L19" s="1" t="s">
+      <x:c r="L19" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M19" s="1" t="str">
+      <x:c r="M19" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N19),IF(N19&lt;R19,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N19" s="39" t="n">
+      <x:c r="N19" s="131" t="n">
         <x:v>1082</x:v>
       </x:c>
-      <x:c r="P19" s="29" t="n">
+      <x:c r="O19" s="167"/>
+      <x:c r="P19" s="131" t="n">
         <x:f>ROUNDUP(G19*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q19" s="30"/>
-      <x:c r="R19" s="29" t="n">
+      <x:c r="Q19" s="178"/>
+      <x:c r="R19" s="131" t="n">
         <x:f>IF(Q19="",P19,MAX(P19,Q19))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S19" s="31" t="n">
+      <x:c r="S19" s="168" t="n">
         <x:f>IF(ISNUMBER(H19),R19*H19,"")</x:f>
         <x:v>8.94</x:v>
       </x:c>
-      <x:c r="T19" s="26" t="str">
+      <x:c r="T19" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U19" s="27" t="str">
+      <x:c r="U19" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W19" s="27" t="str">
+      <x:c r="V19" s="142"/>
+      <x:c r="W19" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X19" s="38" t="d">
+      <x:c r="X19" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y19" s="27" t="str">
+      <x:c r="Y19" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" hidden="0" customHeight="1">
-      <x:c r="A20" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B20" s="15" t="str">
+    <x:row r="20" ht="28" hidden="0" customHeight="1">
+      <x:c r="A20" s="179" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B20" s="179" t="str">
         <x:v>SMBJ18CA (4S TVS)</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="C20" s="179" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D20" s="179" t="str">
         <x:v>SMBJ18CA</x:v>
       </x:c>
-      <x:c r="E20" s="16" t="s">
+      <x:c r="E20" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F20" s="17" t="n">
+      <x:c r="F20" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G20" s="17" t="n">
+      <x:c r="G20" s="170" t="n">
         <x:f aca="0">F20*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H20" s="18">
+      <x:c r="H20" s="171">
         <x:f aca="0"/>
       </x:c>
-      <x:c r="I20" s="19" t="str">
+      <x:c r="I20" s="172" t="str">
         <x:f aca="0">IF(ISNUMBER(H20),F20*H20,"")</x:f>
       </x:c>
-      <x:c r="J20" s="19" t="str">
+      <x:c r="J20" s="172" t="str">
         <x:f aca="0">IF(ISNUMBER(H20),G20*H20,"")</x:f>
       </x:c>
-      <x:c r="K20" s="20" t="str">
+      <x:c r="K20" s="169" t="str">
         <x:v>Updated part: quote required</x:v>
       </x:c>
-      <x:c r="L20" s="16" t="str">
+      <x:c r="L20" s="169" t="str">
         <x:v>Unquoted replacement</x:v>
       </x:c>
-      <x:c r="M20" s="16" t="str">
+      <x:c r="M20" s="179" t="str">
         <x:v>Stock unconfirmed</x:v>
       </x:c>
-      <x:c r="N20" s="40"/>
-      <x:c r="P20" s="29" t="n">
+      <x:c r="N20" s="170"/>
+      <x:c r="O20" s="167"/>
+      <x:c r="P20" s="170" t="n">
         <x:f>ROUNDUP(G20*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q20" s="30"/>
-      <x:c r="R20" s="29" t="n">
+      <x:c r="Q20" s="178"/>
+      <x:c r="R20" s="170" t="n">
         <x:f>IF(Q20="",P20,MAX(P20,Q20))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S20" s="31" t="str">
+      <x:c r="S20" s="177" t="str">
         <x:f>IF(ISNUMBER(H20),R20*H20,"")</x:f>
       </x:c>
-      <x:c r="T20" s="26" t="str">
+      <x:c r="T20" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U20" s="27" t="str">
+      <x:c r="U20" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W20" s="27" t="str">
+      <x:c r="V20" s="142"/>
+      <x:c r="W20" s="175" t="str">
         <x:v>Replacement; sourcing unverified</x:v>
       </x:c>
-      <x:c r="X20" s="38"/>
-      <x:c r="Y20" s="27" t="str">
+      <x:c r="X20" s="176"/>
+      <x:c r="Y20" s="175" t="str">
         <x:v>Previous part price/stock no longer applies. Source: https://www.bourns.com/docs/product-datasheets/smbj.pdf</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" hidden="0" customHeight="1">
-      <x:c r="A21" s="10" t="s">
+    <x:row r="21" ht="28" hidden="0" customHeight="1">
+      <x:c r="A21" s="130" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B21" s="130" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C21" s="130" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B21" s="10" t="s">
+      <x:c r="D21" s="130" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C21" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
+      <x:c r="E21" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="n">
+      <x:c r="F21" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="n">
+      <x:c r="G21" s="131" t="n">
         <x:f aca="0">F21*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H21" s="12" t="n">
+      <x:c r="H21" s="132" t="n">
         <x:f aca="0">IF(R21&gt;=100,0.7534,IF(R21&gt;=25,0.8864,IF(R21&gt;=10,0.989,1.31)))</x:f>
         <x:v>1.31</x:v>
       </x:c>
-      <x:c r="I21" s="13" t="n">
+      <x:c r="I21" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H21),F21*H21,"")</x:f>
         <x:v>1.31</x:v>
       </x:c>
-      <x:c r="J21" s="13" t="n">
+      <x:c r="J21" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H21),G21*H21,"")</x:f>
         <x:v>6.550000000000001</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="s">
+      <x:c r="K21" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L21" s="1" t="s">
+      <x:c r="L21" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M21" s="1" t="str">
+      <x:c r="M21" s="130" t="str">
         <x:f>IF(ISNUMBER(N21),IF(N21&lt;R21,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N21" s="39" t="n">
+      <x:c r="N21" s="131" t="n">
         <x:v>107196</x:v>
       </x:c>
-      <x:c r="P21" s="29" t="n">
+      <x:c r="O21" s="167"/>
+      <x:c r="P21" s="131" t="n">
         <x:f>ROUNDUP(G21*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q21" s="30"/>
-      <x:c r="R21" s="29" t="n">
+      <x:c r="Q21" s="178"/>
+      <x:c r="R21" s="131" t="n">
         <x:f>IF(Q21="",P21,MAX(P21,Q21))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S21" s="31" t="n">
+      <x:c r="S21" s="168" t="n">
         <x:f>IF(ISNUMBER(H21),R21*H21,"")</x:f>
         <x:v>7.86</x:v>
       </x:c>
-      <x:c r="T21" s="26" t="str">
+      <x:c r="T21" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U21" s="27" t="str">
+      <x:c r="U21" s="142" t="str">
         <x:v>Confirm packaging and manual assembly with the team.</x:v>
       </x:c>
-      <x:c r="W21" s="27" t="str">
+      <x:c r="V21" s="142"/>
+      <x:c r="W21" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X21" s="38" t="d">
+      <x:c r="X21" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y21" s="27" t="str">
+      <x:c r="Y21" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" hidden="0" customHeight="1">
-      <x:c r="A22" s="15" t="s">
+    <x:row r="22" ht="28" hidden="0" customHeight="1">
+      <x:c r="A22" s="179" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B22" s="179" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C22" s="179" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B22" s="15" t="s">
+      <x:c r="D22" s="179" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
+      <x:c r="E22" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F22" s="17" t="n">
+      <x:c r="F22" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G22" s="17" t="n">
+      <x:c r="G22" s="170" t="n">
         <x:f aca="0">F22*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H22" s="18" t="n">
+      <x:c r="H22" s="171" t="n">
         <x:f aca="0">IF(R22&gt;=100,0.7584,IF(R22&gt;=50,0.822,IF(R22&gt;=10,0.991,IF(R22&gt;=5,1.074,1.3))))</x:f>
         <x:v>1.074</x:v>
       </x:c>
-      <x:c r="I22" s="19" t="n">
+      <x:c r="I22" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H22),F22*H22,"")</x:f>
         <x:v>1.074</x:v>
       </x:c>
-      <x:c r="J22" s="19" t="n">
+      <x:c r="J22" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H22),G22*H22,"")</x:f>
         <x:v>5.37</x:v>
       </x:c>
-      <x:c r="K22" s="20" t="s">
+      <x:c r="K22" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L22" s="16" t="s">
+      <x:c r="L22" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M22" s="16" t="str">
+      <x:c r="M22" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N22),IF(N22&lt;R22,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N22" s="40" t="n">
+      <x:c r="N22" s="170" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="P22" s="29" t="n">
+      <x:c r="O22" s="167"/>
+      <x:c r="P22" s="170" t="n">
         <x:f>ROUNDUP(G22*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q22" s="30"/>
-      <x:c r="R22" s="29" t="n">
+      <x:c r="Q22" s="178"/>
+      <x:c r="R22" s="170" t="n">
         <x:f>IF(Q22="",P22,MAX(P22,Q22))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S22" s="31" t="n">
+      <x:c r="S22" s="177" t="n">
         <x:f>IF(ISNUMBER(H22),R22*H22,"")</x:f>
         <x:v>6.444000000000001</x:v>
       </x:c>
-      <x:c r="T22" s="26" t="str">
+      <x:c r="T22" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U22" s="27" t="str">
+      <x:c r="U22" s="175" t="str">
         <x:v>Confirm packaging and manual assembly with the team.</x:v>
       </x:c>
-      <x:c r="W22" s="27" t="str">
+      <x:c r="V22" s="142"/>
+      <x:c r="W22" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X22" s="38" t="d">
+      <x:c r="X22" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y22" s="27" t="str">
+      <x:c r="Y22" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="27" hidden="0" customHeight="1">
-      <x:c r="A23" s="10" t="s">
+    <x:row r="23" ht="28" hidden="0" customHeight="1">
+      <x:c r="A23" s="130" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B23" s="130" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C23" s="130" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B23" s="10" t="s">
+      <x:c r="D23" s="130" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E23" s="122" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C23" s="10" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D23" s="10" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="n">
+      <x:c r="F23" s="131" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="n">
+      <x:c r="G23" s="131" t="n">
         <x:f aca="0">F23*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H23" s="12" t="n">
+      <x:c r="H23" s="132" t="n">
         <x:f aca="0"/>
         <x:v>0.6464</x:v>
       </x:c>
-      <x:c r="I23" s="13" t="n">
+      <x:c r="I23" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H23),F23*H23,"")</x:f>
         <x:v>1.2928</x:v>
       </x:c>
-      <x:c r="J23" s="13" t="n">
+      <x:c r="J23" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H23),G23*H23,"")</x:f>
         <x:v>6.4639999999999995</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="L23" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="M23" s="1" t="str">
+      <x:c r="K23" s="122" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L23" s="122" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M23" s="130" t="str">
         <x:f>IF(ISNUMBER(N23),IF(N23&lt;SUM(R23,R25),"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N23" s="39" t="n">
+      <x:c r="N23" s="131" t="n">
         <x:f>N25</x:f>
         <x:v>5918</x:v>
       </x:c>
-      <x:c r="P23" s="29" t="n">
+      <x:c r="O23" s="167"/>
+      <x:c r="P23" s="131" t="n">
         <x:f>ROUNDUP(G23*1.2,0)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="Q23" s="30"/>
-      <x:c r="R23" s="29" t="n">
+      <x:c r="Q23" s="178"/>
+      <x:c r="R23" s="131" t="n">
         <x:f>IF(Q23="",P23,MAX(P23,Q23))</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="S23" s="31" t="n">
+      <x:c r="S23" s="168" t="n">
         <x:f>IF(ISNUMBER(H23),R23*H23,"")</x:f>
         <x:v>7.7568</x:v>
       </x:c>
-      <x:c r="T23" s="26" t="str">
+      <x:c r="T23" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U23" s="27" t="str">
+      <x:c r="U23" s="142" t="str">
         <x:v>XT60PW-F: 45 A rated / 60 A momentary (duration unspecified). Confirm manual THT soldering and cable polarity.</x:v>
       </x:c>
-      <x:c r="W23" s="27" t="str">
+      <x:c r="V23" s="142"/>
+      <x:c r="W23" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X23" s="38" t="d">
+      <x:c r="X23" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y23" s="27" t="str">
+      <x:c r="Y23" s="142" t="str">
         <x:v>Same XT60 stock pool: compare against J1 + J3 + J4 combined order. Price/stock inherited from J4 snapshot; recheck checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="27" hidden="0" customHeight="1">
-      <x:c r="A24" s="15" t="s">
+    <x:row r="24" ht="28" hidden="0" customHeight="1">
+      <x:c r="A24" s="179" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B24" s="179" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C24" s="179" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B24" s="15" t="s">
+      <x:c r="D24" s="179" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="E24" s="169" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E24" s="16" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="n">
+      <x:c r="F24" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G24" s="17" t="n">
+      <x:c r="G24" s="170" t="n">
         <x:f aca="0">F24*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H24" s="18" t="n">
+      <x:c r="H24" s="171" t="n">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="I24" s="19" t="n">
+      <x:c r="I24" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H24),F24*H24,"")</x:f>
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="J24" s="19" t="n">
+      <x:c r="J24" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H24),G24*H24,"")</x:f>
         <x:v>1.9</x:v>
       </x:c>
-      <x:c r="K24" s="20" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="L24" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="M24" s="16" t="str">
+      <x:c r="K24" s="169" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L24" s="169" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M24" s="179" t="str">
         <x:f>IF(ISNUMBER(N24),IF(N24&lt;R24,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Stock unconfirmed</x:v>
       </x:c>
-      <x:c r="N24" s="40"/>
-      <x:c r="P24" s="29" t="n">
+      <x:c r="N24" s="170"/>
+      <x:c r="O24" s="167"/>
+      <x:c r="P24" s="170" t="n">
         <x:f>ROUNDUP(G24*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q24" s="30"/>
-      <x:c r="R24" s="29" t="n">
+      <x:c r="Q24" s="178"/>
+      <x:c r="R24" s="170" t="n">
         <x:f>IF(Q24="",P24,MAX(P24,Q24))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S24" s="31" t="n">
+      <x:c r="S24" s="177" t="n">
         <x:f>IF(ISNUMBER(H24),R24*H24,"")</x:f>
         <x:v>2.2800000000000002</x:v>
       </x:c>
-      <x:c r="T24" s="26" t="str">
+      <x:c r="T24" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U24" s="27" t="str">
+      <x:c r="U24" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel/equivalent with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W24" s="27" t="str">
+      <x:c r="V24" s="142"/>
+      <x:c r="W24" s="175" t="str">
         <x:v>Repaired; page unverified</x:v>
       </x:c>
-      <x:c r="X24" s="38" t="d">
+      <x:c r="X24" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y24" s="27" t="str">
+      <x:c r="Y24" s="175" t="str">
         <x:v>US page unreadable. Regional pages conflict: 0 vs 963. Ask Mouser to confirm US stock.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="27" hidden="0" customHeight="1">
-      <x:c r="A25" s="10" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B25" s="10" t="s">
+    <x:row r="25" ht="28" hidden="0" customHeight="1">
+      <x:c r="A25" s="130" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B25" s="130" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C25" s="130" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D25" s="130" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E25" s="122" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C25" s="10" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D25" s="10" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="n">
+      <x:c r="F25" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="n">
+      <x:c r="G25" s="131" t="n">
         <x:f aca="0">F25*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H25" s="12" t="n">
+      <x:c r="H25" s="132" t="n">
         <x:v>0.6464</x:v>
       </x:c>
-      <x:c r="I25" s="13" t="n">
+      <x:c r="I25" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H25),F25*H25,"")</x:f>
         <x:v>0.6464</x:v>
       </x:c>
-      <x:c r="J25" s="13" t="n">
+      <x:c r="J25" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H25),G25*H25,"")</x:f>
         <x:v>3.2319999999999998</x:v>
       </x:c>
-      <x:c r="K25" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="L25" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="M25" s="1" t="str">
+      <x:c r="K25" s="122" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L25" s="122" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M25" s="130" t="str">
         <x:f>IF(ISNUMBER(N25),IF(N25&lt;SUM(R23,R25),"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N25" s="39" t="n">
+      <x:c r="N25" s="131" t="n">
         <x:v>5918</x:v>
       </x:c>
-      <x:c r="P25" s="29" t="n">
+      <x:c r="O25" s="167"/>
+      <x:c r="P25" s="131" t="n">
         <x:f>ROUNDUP(G25*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q25" s="30"/>
-      <x:c r="R25" s="29" t="n">
+      <x:c r="Q25" s="178"/>
+      <x:c r="R25" s="131" t="n">
         <x:f>IF(Q25="",P25,MAX(P25,Q25))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S25" s="31" t="n">
+      <x:c r="S25" s="168" t="n">
         <x:f>IF(ISNUMBER(H25),R25*H25,"")</x:f>
         <x:v>3.8784</x:v>
       </x:c>
-      <x:c r="T25" s="26" t="str">
+      <x:c r="T25" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U25" s="27" t="str">
+      <x:c r="U25" s="142" t="str">
         <x:v>XT60PW-F: 45 A rated / 60 A momentary (duration unspecified). Confirm manual THT soldering and cable polarity.</x:v>
       </x:c>
-      <x:c r="W25" s="27" t="str">
+      <x:c r="V25" s="142"/>
+      <x:c r="W25" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X25" s="38" t="d">
+      <x:c r="X25" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y25" s="27" t="str">
+      <x:c r="Y25" s="142" t="str">
         <x:v>Same XT60 stock pool: compare against J1 + J3 + J4 combined order. Price/stock inherited from J4 snapshot; recheck checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="27" hidden="0" customHeight="1">
-      <x:c r="A26" s="15" t="s">
+    <x:row r="26" ht="28" hidden="0" customHeight="1">
+      <x:c r="A26" s="179" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B26" s="179" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C26" s="179" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B26" s="15" t="s">
+      <x:c r="D26" s="179" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E26" s="16" t="s">
+      <x:c r="E26" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F26" s="17" t="n">
+      <x:c r="F26" s="170" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G26" s="17" t="n">
+      <x:c r="G26" s="170" t="n">
         <x:f aca="0">F26*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H26" s="18" t="n">
+      <x:c r="H26" s="171" t="n">
         <x:f aca="0">IF(R26&gt;=500,1.64208,IF(R26&gt;=100,1.9816,IF(R26&gt;=50,2.1878,IF(R26&gt;=10,2.828,4.32))))</x:f>
         <x:v>2.828</x:v>
       </x:c>
-      <x:c r="I26" s="19" t="n">
+      <x:c r="I26" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H26),F26*H26,"")</x:f>
         <x:v>5.656</x:v>
       </x:c>
-      <x:c r="J26" s="19" t="n">
+      <x:c r="J26" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H26),G26*H26,"")</x:f>
         <x:v>28.279999999999998</x:v>
       </x:c>
-      <x:c r="K26" s="20" t="s">
+      <x:c r="K26" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L26" s="16" t="s">
+      <x:c r="L26" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M26" s="16" t="str">
+      <x:c r="M26" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N26),IF(N26&lt;R26,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N26" s="40" t="n">
+      <x:c r="N26" s="170" t="n">
         <x:v>5063</x:v>
       </x:c>
-      <x:c r="P26" s="29" t="n">
+      <x:c r="O26" s="167"/>
+      <x:c r="P26" s="170" t="n">
         <x:f>ROUNDUP(G26*1.2,0)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="Q26" s="30"/>
-      <x:c r="R26" s="29" t="n">
+      <x:c r="Q26" s="178"/>
+      <x:c r="R26" s="170" t="n">
         <x:f>IF(Q26="",P26,MAX(P26,Q26))</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="S26" s="31" t="n">
+      <x:c r="S26" s="177" t="n">
         <x:f>IF(ISNUMBER(H26),R26*H26,"")</x:f>
         <x:v>33.936</x:v>
       </x:c>
-      <x:c r="T26" s="26" t="str">
+      <x:c r="T26" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U26" s="27" t="str">
+      <x:c r="U26" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W26" s="27" t="str">
+      <x:c r="V26" s="142"/>
+      <x:c r="W26" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X26" s="38" t="d">
+      <x:c r="X26" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y26" s="27" t="str">
+      <x:c r="Y26" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="27" hidden="0" customHeight="1">
-      <x:c r="A27" s="10" t="s">
+    <x:row r="27" ht="28" hidden="0" customHeight="1">
+      <x:c r="A27" s="130" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B27" s="130" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C27" s="130" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D27" s="130" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B27" s="10" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C27" s="10" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D27" s="10" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
+      <x:c r="E27" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="n">
+      <x:c r="F27" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="n">
+      <x:c r="G27" s="131" t="n">
         <x:f aca="0">F27*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H27" s="12" t="n">
+      <x:c r="H27" s="132" t="n">
         <x:f aca="0">IF(R27&gt;=100,0.9996,IF(R27&gt;=50,1.1164,IF(R27&gt;=10,1.478,2.32)))</x:f>
         <x:v>2.32</x:v>
       </x:c>
-      <x:c r="I27" s="13" t="n">
+      <x:c r="I27" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H27),F27*H27,"")</x:f>
         <x:v>2.32</x:v>
       </x:c>
-      <x:c r="J27" s="13" t="n">
+      <x:c r="J27" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H27),G27*H27,"")</x:f>
         <x:v>11.6</x:v>
       </x:c>
-      <x:c r="K27" s="14" t="s">
+      <x:c r="K27" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L27" s="1" t="s">
+      <x:c r="L27" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M27" s="1" t="str">
+      <x:c r="M27" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N27),IF(N27&lt;R27,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N27" s="39" t="n">
+      <x:c r="N27" s="131" t="n">
         <x:v>9627</x:v>
       </x:c>
-      <x:c r="P27" s="29" t="n">
+      <x:c r="O27" s="167"/>
+      <x:c r="P27" s="131" t="n">
         <x:f>ROUNDUP(G27*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q27" s="30"/>
-      <x:c r="R27" s="29" t="n">
+      <x:c r="Q27" s="178"/>
+      <x:c r="R27" s="131" t="n">
         <x:f>IF(Q27="",P27,MAX(P27,Q27))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S27" s="31" t="n">
+      <x:c r="S27" s="168" t="n">
         <x:f>IF(ISNUMBER(H27),R27*H27,"")</x:f>
         <x:v>13.919999999999998</x:v>
       </x:c>
-      <x:c r="T27" s="26" t="str">
+      <x:c r="T27" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U27" s="27" t="str">
+      <x:c r="U27" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W27" s="27" t="str">
+      <x:c r="V27" s="142"/>
+      <x:c r="W27" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X27" s="38" t="d">
+      <x:c r="X27" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y27" s="27" t="str">
+      <x:c r="Y27" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="27" hidden="0" customHeight="1">
-      <x:c r="A28" s="15" t="s">
+    <x:row r="28" ht="28" hidden="0" customHeight="1">
+      <x:c r="A28" s="179" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B28" s="179" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C28" s="179" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B28" s="15" t="s">
+      <x:c r="D28" s="179" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E28" s="16" t="s">
+      <x:c r="E28" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F28" s="17" t="n">
+      <x:c r="F28" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G28" s="17" t="n">
+      <x:c r="G28" s="170" t="n">
         <x:f aca="0">F28*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H28" s="18" t="n">
+      <x:c r="H28" s="171" t="n">
         <x:f aca="0">IF(R28&gt;=1000,0.00973,IF(R28&gt;=500,0.01136,IF(R28&gt;=250,0.01344,IF(R28&gt;=100,0.0171,IF(R28&gt;=50,0.0208,IF(R28&gt;=25,0.0256,IF(R28&gt;=10,0.034,0.1)))))))</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="I28" s="19" t="n">
+      <x:c r="I28" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H28),F28*H28,"")</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="J28" s="19" t="n">
+      <x:c r="J28" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H28),G28*H28,"")</x:f>
         <x:v>0.0855</x:v>
       </x:c>
-      <x:c r="K28" s="20" t="s">
+      <x:c r="K28" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L28" s="16" t="s">
+      <x:c r="L28" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M28" s="16" t="str">
+      <x:c r="M28" s="179" t="str">
         <x:f>IF(ISNUMBER(N28),IF(N28&lt;R28,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N28" s="40" t="n">
+      <x:c r="N28" s="170" t="n">
         <x:v>131437</x:v>
       </x:c>
-      <x:c r="P28" s="29" t="n">
+      <x:c r="O28" s="167"/>
+      <x:c r="P28" s="170" t="n">
         <x:f>IF(G28=0,0,MAX(100,10*G28))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q28" s="30"/>
-      <x:c r="R28" s="29" t="n">
+      <x:c r="Q28" s="178"/>
+      <x:c r="R28" s="170" t="n">
         <x:f>IF(Q28="",P28,MAX(P28,Q28))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S28" s="31" t="n">
+      <x:c r="S28" s="177" t="n">
         <x:f>IF(ISNUMBER(H28),R28*H28,"")</x:f>
         <x:v>1.71</x:v>
       </x:c>
-      <x:c r="T28" s="26" t="str">
+      <x:c r="T28" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U28" s="27" t="str">
+      <x:c r="U28" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W28" s="27" t="str">
+      <x:c r="V28" s="142"/>
+      <x:c r="W28" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X28" s="38" t="d">
+      <x:c r="X28" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y28" s="27" t="str">
+      <x:c r="Y28" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="27" hidden="0" customHeight="1">
-      <x:c r="A29" s="10" t="s">
+    <x:row r="29" ht="28" hidden="0" customHeight="1">
+      <x:c r="A29" s="130" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B29" s="130" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C29" s="130" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D29" s="130" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B29" s="10" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D29" s="10" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
+      <x:c r="E29" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="n">
+      <x:c r="F29" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G29" s="11" t="n">
+      <x:c r="G29" s="131" t="n">
         <x:f aca="0">F29*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H29" s="12" t="n">
+      <x:c r="H29" s="132" t="n">
         <x:f aca="0">IF(R29&gt;=1000,0.00973,IF(R29&gt;=500,0.01136,IF(R29&gt;=250,0.01344,IF(R29&gt;=100,0.0171,IF(R29&gt;=50,0.0208,IF(R29&gt;=25,0.0256,IF(R29&gt;=10,0.034,0.1)))))))</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="I29" s="13" t="n">
+      <x:c r="I29" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H29),F29*H29,"")</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="J29" s="13" t="n">
+      <x:c r="J29" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H29),G29*H29,"")</x:f>
         <x:v>0.0855</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="s">
+      <x:c r="K29" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L29" s="1" t="s">
+      <x:c r="L29" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M29" s="1" t="str">
+      <x:c r="M29" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N29),IF(N29&lt;R29,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N29" s="39" t="n">
+      <x:c r="N29" s="131" t="n">
         <x:v>38419</x:v>
       </x:c>
-      <x:c r="P29" s="29" t="n">
+      <x:c r="O29" s="167"/>
+      <x:c r="P29" s="131" t="n">
         <x:f>IF(G29=0,0,MAX(100,10*G29))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q29" s="30"/>
-      <x:c r="R29" s="29" t="n">
+      <x:c r="Q29" s="178"/>
+      <x:c r="R29" s="131" t="n">
         <x:f>IF(Q29="",P29,MAX(P29,Q29))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S29" s="31" t="n">
+      <x:c r="S29" s="168" t="n">
         <x:f>IF(ISNUMBER(H29),R29*H29,"")</x:f>
         <x:v>1.71</x:v>
       </x:c>
-      <x:c r="T29" s="26" t="str">
+      <x:c r="T29" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U29" s="27" t="str">
+      <x:c r="U29" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W29" s="27" t="str">
+      <x:c r="V29" s="142"/>
+      <x:c r="W29" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X29" s="38" t="d">
+      <x:c r="X29" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y29" s="27" t="str">
+      <x:c r="Y29" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="27" hidden="0" customHeight="1">
-      <x:c r="A30" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B30" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E30" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="n">
+    <x:row r="30" ht="28" hidden="0" customHeight="1">
+      <x:c r="A30" s="179" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B30" s="179" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C30" s="179" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D30" s="179" t="str">
+        <x:v>0805W8F2004T5E</x:v>
+      </x:c>
+      <x:c r="E30" s="169" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F30" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G30" s="17" t="n">
+      <x:c r="G30" s="170" t="n">
         <x:f aca="0">F30*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H30" s="18" t="n">
-        <x:f aca="0">IF(R30&gt;=1000,0.01032,IF(R30&gt;=500,0.01204,IF(R30&gt;=250,0.01424,IF(R30&gt;=100,0.0181,IF(R30&gt;=50,0.022,IF(R30&gt;=25,0.0272,IF(R30&gt;=10,0.036,0.11)))))))</x:f>
-        <x:v>0.0181</x:v>
-      </x:c>
-      <x:c r="I30" s="19" t="n">
+      <x:c r="H30" s="171" t="n">
+        <x:f aca="0">IF(R30&gt;=100000,0.0037,IF(R30&gt;=50000,0.0039,IF(R30&gt;=10000,0.0043,IF(R30&gt;=5000,0.0047,IF(R30&gt;=1000,0.0057,0.007)))))</x:f>
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="I30" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H30),F30*H30,"")</x:f>
-        <x:v>0.0181</x:v>
-      </x:c>
-      <x:c r="J30" s="19" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="J30" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H30),G30*H30,"")</x:f>
-        <x:v>0.09050000000000001</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L30" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M30" s="16" t="str">
+        <x:v>0.035</x:v>
+      </x:c>
+      <x:c r="K30" s="169" t="str">
+        <x:v>LCSC C26112</x:v>
+      </x:c>
+      <x:c r="L30" s="169" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M30" s="179" t="str">
         <x:f>IF(ISNUMBER(N30),IF(N30&lt;R30,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N30" s="40" t="n">
-        <x:v>30217</x:v>
-      </x:c>
-      <x:c r="P30" s="29" t="n">
-        <x:f>IF(G30=0,0,MAX(100,10*G30))</x:f>
+      <x:c r="N30" s="170" t="n">
+        <x:v>17200</x:v>
+      </x:c>
+      <x:c r="O30" s="167"/>
+      <x:c r="P30" s="170" t="n">
+        <x:f>IF(G30=0,0,CEILING(MAX(100,10*G30),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q30" s="30"/>
-      <x:c r="R30" s="29" t="n">
-        <x:f>IF(Q30="",P30,MAX(P30,Q30))</x:f>
+      <x:c r="Q30" s="178"/>
+      <x:c r="R30" s="170" t="n">
+        <x:f>IF(Q30="",P30,CEILING(MAX(P30,Q30),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S30" s="31" t="n">
+      <x:c r="S30" s="177" t="n">
         <x:f>IF(ISNUMBER(H30),R30*H30,"")</x:f>
-        <x:v>1.81</x:v>
-      </x:c>
-      <x:c r="T30" s="26" t="str">
+        <x:v>0.7000000000000001</x:v>
+      </x:c>
+      <x:c r="T30" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U30" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W30" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X30" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y30" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="27" hidden="0" customHeight="1">
-      <x:c r="A31" s="10" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B31" s="10" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C31" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D31" s="10" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="n">
+      <x:c r="U30" s="175" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C26112. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V30" s="142"/>
+      <x:c r="W30" s="175" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X30" s="191" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y30" s="175" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C26112.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="28" hidden="0" customHeight="1">
+      <x:c r="A31" s="130" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B31" s="130" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C31" s="130" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D31" s="130" t="str">
+        <x:v>0805W8F2202T5E</x:v>
+      </x:c>
+      <x:c r="E31" s="122" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F31" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G31" s="11" t="n">
+      <x:c r="G31" s="131" t="n">
         <x:f aca="0">F31*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H31" s="12" t="n">
-        <x:f aca="0">IF(R31&gt;=1000,0.00973,IF(R31&gt;=500,0.01136,IF(R31&gt;=250,0.01344,IF(R31&gt;=100,0.0171,IF(R31&gt;=50,0.0208,IF(R31&gt;=25,0.0256,IF(R31&gt;=10,0.034,0.1)))))))</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="I31" s="13" t="n">
+      <x:c r="H31" s="132" t="n">
+        <x:f aca="0">IF(R31&gt;=100000,0.0023,IF(R31&gt;=50000,0.0025,IF(R31&gt;=10000,0.0028,IF(R31&gt;=5000,0.0031,IF(R31&gt;=1000,0.0039,0.0048)))))</x:f>
+        <x:v>0.0048</x:v>
+      </x:c>
+      <x:c r="I31" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H31),F31*H31,"")</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="J31" s="13" t="n">
+        <x:v>0.0048</x:v>
+      </x:c>
+      <x:c r="J31" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H31),G31*H31,"")</x:f>
-        <x:v>0.0855</x:v>
-      </x:c>
-      <x:c r="K31" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L31" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M31" s="1" t="str">
+        <x:v>0.023999999999999997</x:v>
+      </x:c>
+      <x:c r="K31" s="122" t="str">
+        <x:v>LCSC C17560</x:v>
+      </x:c>
+      <x:c r="L31" s="122" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M31" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N31),IF(N31&lt;R31,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N31" s="39" t="n">
-        <x:v>246713</x:v>
-      </x:c>
-      <x:c r="P31" s="29" t="n">
-        <x:f>IF(G31=0,0,MAX(100,10*G31))</x:f>
+      <x:c r="N31" s="131" t="n">
+        <x:v>1226000</x:v>
+      </x:c>
+      <x:c r="O31" s="167"/>
+      <x:c r="P31" s="131" t="n">
+        <x:f>IF(G31=0,0,CEILING(MAX(100,10*G31),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q31" s="30"/>
-      <x:c r="R31" s="29" t="n">
-        <x:f>IF(Q31="",P31,MAX(P31,Q31))</x:f>
+      <x:c r="Q31" s="178"/>
+      <x:c r="R31" s="131" t="n">
+        <x:f>IF(Q31="",P31,CEILING(MAX(P31,Q31),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S31" s="31" t="n">
+      <x:c r="S31" s="168" t="n">
         <x:f>IF(ISNUMBER(H31),R31*H31,"")</x:f>
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="T31" s="26" t="str">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="T31" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U31" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W31" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X31" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y31" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="27" hidden="0" customHeight="1">
-      <x:c r="A32" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B32" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E32" s="16" t="s">
+      <x:c r="U31" s="142" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17560. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V31" s="142"/>
+      <x:c r="W31" s="142" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X31" s="192" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y31" s="142" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17560.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="28" hidden="0" customHeight="1">
+      <x:c r="A32" s="179" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B32" s="179" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C32" s="179" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D32" s="179" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E32" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F32" s="17" t="n">
+      <x:c r="F32" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G32" s="17" t="n">
+      <x:c r="G32" s="170" t="n">
         <x:f aca="0">F32*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H32" s="18" t="n">
+      <x:c r="H32" s="171" t="n">
         <x:f aca="0">IF(R32&gt;=500,0.98808,IF(R32&gt;=250,1.0732,IF(R32&gt;=100,1.2092,IF(R32&gt;=50,1.3334,IF(R32&gt;=25,1.4792,IF(R32&gt;=10,1.712,2.57))))))</x:f>
         <x:v>1.2092</x:v>
       </x:c>
-      <x:c r="I32" s="19" t="n">
+      <x:c r="I32" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H32),F32*H32,"")</x:f>
         <x:v>1.2092</x:v>
       </x:c>
-      <x:c r="J32" s="19" t="n">
+      <x:c r="J32" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H32),G32*H32,"")</x:f>
         <x:v>6.046</x:v>
       </x:c>
-      <x:c r="K32" s="20" t="s">
+      <x:c r="K32" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L32" s="16" t="s">
+      <x:c r="L32" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M32" s="16" t="str">
+      <x:c r="M32" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N32),IF(N32&lt;R32,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N32" s="40" t="n">
+      <x:c r="N32" s="170" t="n">
         <x:v>10405</x:v>
       </x:c>
-      <x:c r="P32" s="29" t="n">
+      <x:c r="O32" s="167"/>
+      <x:c r="P32" s="170" t="n">
         <x:f>IF(G32=0,0,MAX(100,10*G32))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q32" s="30"/>
-      <x:c r="R32" s="29" t="n">
+      <x:c r="Q32" s="178"/>
+      <x:c r="R32" s="170" t="n">
         <x:f>IF(Q32="",P32,MAX(P32,Q32))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S32" s="31" t="n">
+      <x:c r="S32" s="177" t="n">
         <x:f>IF(ISNUMBER(H32),R32*H32,"")</x:f>
         <x:v>120.92</x:v>
       </x:c>
-      <x:c r="T32" s="26" t="str">
+      <x:c r="T32" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U32" s="27" t="str">
+      <x:c r="U32" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W32" s="27" t="str">
+      <x:c r="V32" s="142"/>
+      <x:c r="W32" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X32" s="38" t="d">
+      <x:c r="X32" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y32" s="27" t="str">
+      <x:c r="Y32" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="27" hidden="0" customHeight="1">
-      <x:c r="A33" s="10" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B33" s="10" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C33" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D33" s="10" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="n">
+    <x:row r="33" ht="28" hidden="0" customHeight="1">
+      <x:c r="A33" s="130" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B33" s="130" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C33" s="130" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D33" s="130" t="str">
+        <x:v>0805W8F6803T5E</x:v>
+      </x:c>
+      <x:c r="E33" s="122" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F33" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G33" s="11" t="n">
+      <x:c r="G33" s="131" t="n">
         <x:f aca="0">F33*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H33" s="12" t="n">
-        <x:f aca="0">IF(R33&gt;=1000,0.01032,IF(R33&gt;=500,0.01204,IF(R33&gt;=250,0.01424,IF(R33&gt;=100,0.0181,IF(R33&gt;=50,0.022,IF(R33&gt;=25,0.0272,IF(R33&gt;=10,0.036,0.11)))))))</x:f>
-        <x:v>0.0181</x:v>
-      </x:c>
-      <x:c r="I33" s="13" t="n">
+      <x:c r="H33" s="132" t="n">
+        <x:f aca="0">IF(R33&gt;=50000,0.0021,IF(R33&gt;=10000,0.0024,IF(R33&gt;=5000,0.0026,IF(R33&gt;=1000,0.0033,0.0042))))</x:f>
+        <x:v>0.0042</x:v>
+      </x:c>
+      <x:c r="I33" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H33),F33*H33,"")</x:f>
-        <x:v>0.0181</x:v>
-      </x:c>
-      <x:c r="J33" s="13" t="n">
+        <x:v>0.0042</x:v>
+      </x:c>
+      <x:c r="J33" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H33),G33*H33,"")</x:f>
-        <x:v>0.09050000000000001</x:v>
-      </x:c>
-      <x:c r="K33" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L33" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M33" s="1" t="str">
+        <x:v>0.020999999999999998</x:v>
+      </x:c>
+      <x:c r="K33" s="122" t="str">
+        <x:v>LCSC C17797</x:v>
+      </x:c>
+      <x:c r="L33" s="122" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M33" s="130" t="str">
         <x:f>IF(ISNUMBER(N33),IF(N33&lt;R33,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N33" s="39" t="n">
-        <x:v>6977</x:v>
-      </x:c>
-      <x:c r="P33" s="29" t="n">
-        <x:f>IF(G33=0,0,MAX(100,10*G33))</x:f>
+      <x:c r="N33" s="131" t="n">
+        <x:v>64300</x:v>
+      </x:c>
+      <x:c r="O33" s="167"/>
+      <x:c r="P33" s="131" t="n">
+        <x:f>IF(G33=0,0,CEILING(MAX(100,10*G33),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q33" s="30"/>
-      <x:c r="R33" s="29" t="n">
-        <x:f>IF(Q33="",P33,MAX(P33,Q33))</x:f>
+      <x:c r="Q33" s="178"/>
+      <x:c r="R33" s="131" t="n">
+        <x:f>IF(Q33="",P33,CEILING(MAX(P33,Q33),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S33" s="31" t="n">
+      <x:c r="S33" s="168" t="n">
         <x:f>IF(ISNUMBER(H33),R33*H33,"")</x:f>
-        <x:v>1.81</x:v>
-      </x:c>
-      <x:c r="T33" s="26" t="str">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="T33" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U33" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W33" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X33" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y33" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="27" hidden="0" customHeight="1">
-      <x:c r="A34" s="15" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B34" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E34" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F34" s="17" t="n">
+      <x:c r="U33" s="142" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17797. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V33" s="142"/>
+      <x:c r="W33" s="142" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X33" s="192" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y33" s="142" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17797.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="28" hidden="0" customHeight="1">
+      <x:c r="A34" s="179" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B34" s="179" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C34" s="179" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D34" s="179" t="str">
+        <x:v>0805W8F2003T5E</x:v>
+      </x:c>
+      <x:c r="E34" s="169" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F34" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G34" s="17" t="n">
+      <x:c r="G34" s="170" t="n">
         <x:f aca="0">F34*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H34" s="18" t="n">
-        <x:f aca="0">IF(R34&gt;=1000,0.00973,IF(R34&gt;=500,0.01136,IF(R34&gt;=250,0.01344,IF(R34&gt;=100,0.0171,IF(R34&gt;=50,0.0208,IF(R34&gt;=25,0.0256,IF(R34&gt;=10,0.034,0.1)))))))</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="I34" s="19" t="n">
+      <x:c r="H34" s="171" t="n">
+        <x:f aca="0">IF(R34&gt;=100000,0.0027,IF(R34&gt;=50000,0.0029,IF(R34&gt;=10000,0.0032,IF(R34&gt;=5000,0.0036,IF(R34&gt;=1000,0.0044,0.0056)))))</x:f>
+        <x:v>0.0056</x:v>
+      </x:c>
+      <x:c r="I34" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H34),F34*H34,"")</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="J34" s="19" t="n">
+        <x:v>0.0056</x:v>
+      </x:c>
+      <x:c r="J34" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H34),G34*H34,"")</x:f>
-        <x:v>0.0855</x:v>
-      </x:c>
-      <x:c r="K34" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L34" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M34" s="16" t="str">
+        <x:v>0.028</x:v>
+      </x:c>
+      <x:c r="K34" s="169" t="str">
+        <x:v>LCSC C17539</x:v>
+      </x:c>
+      <x:c r="L34" s="169" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M34" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N34),IF(N34&lt;R34,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N34" s="40" t="n">
-        <x:v>245164</x:v>
-      </x:c>
-      <x:c r="P34" s="29" t="n">
-        <x:f>IF(G34=0,0,MAX(100,10*G34))</x:f>
+      <x:c r="N34" s="170" t="n">
+        <x:v>428200</x:v>
+      </x:c>
+      <x:c r="O34" s="167"/>
+      <x:c r="P34" s="170" t="n">
+        <x:f>IF(G34=0,0,CEILING(MAX(100,10*G34),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q34" s="30"/>
-      <x:c r="R34" s="29" t="n">
-        <x:f>IF(Q34="",P34,MAX(P34,Q34))</x:f>
+      <x:c r="Q34" s="178"/>
+      <x:c r="R34" s="170" t="n">
+        <x:f>IF(Q34="",P34,CEILING(MAX(P34,Q34),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S34" s="31" t="n">
+      <x:c r="S34" s="177" t="n">
         <x:f>IF(ISNUMBER(H34),R34*H34,"")</x:f>
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="T34" s="26" t="str">
+        <x:v>0.5599999999999999</x:v>
+      </x:c>
+      <x:c r="T34" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U34" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W34" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X34" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y34" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="27" hidden="0" customHeight="1">
-      <x:c r="A35" s="10" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B35" s="10" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C35" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D35" s="10" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="n">
+      <x:c r="U34" s="175" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17539. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V34" s="142"/>
+      <x:c r="W34" s="175" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X34" s="191" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y34" s="175" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17539.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="28" hidden="0" customHeight="1">
+      <x:c r="A35" s="130" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B35" s="130" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C35" s="130" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D35" s="130" t="str">
+        <x:v>0805W8F100JT5E</x:v>
+      </x:c>
+      <x:c r="E35" s="122" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F35" s="131" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G35" s="11" t="n">
+      <x:c r="G35" s="131" t="n">
         <x:f aca="0">F35*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H35" s="12" t="n">
-        <x:f aca="0">IF(R35&gt;=1000,0.01767,IF(R35&gt;=500,0.02018,IF(R35&gt;=250,0.02336,IF(R35&gt;=100,0.029,IF(R35&gt;=50,0.0346,IF(R35&gt;=25,0.0416,IF(R35&gt;=10,0.054,0.12)))))))</x:f>
-        <x:v>0.029</x:v>
-      </x:c>
-      <x:c r="I35" s="13" t="n">
+      <x:c r="H35" s="132" t="n">
+        <x:f aca="0">IF(R35&gt;=50000,0.0022,IF(R35&gt;=10000,0.0024,IF(R35&gt;=5000,0.0027,IF(R35&gt;=1000,0.0032,0.004))))</x:f>
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="I35" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H35),F35*H35,"")</x:f>
-        <x:v>0.058</x:v>
-      </x:c>
-      <x:c r="J35" s="13" t="n">
+        <x:v>0.008</x:v>
+      </x:c>
+      <x:c r="J35" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H35),G35*H35,"")</x:f>
-        <x:v>0.29000000000000004</x:v>
-      </x:c>
-      <x:c r="K35" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L35" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M35" s="1" t="str">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="K35" s="122" t="str">
+        <x:v>LCSC C17415</x:v>
+      </x:c>
+      <x:c r="L35" s="122" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M35" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N35),IF(N35&lt;R35,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N35" s="39" t="n">
-        <x:v>732061</x:v>
-      </x:c>
-      <x:c r="P35" s="29" t="n">
-        <x:f>IF(G35=0,0,MAX(100,10*G35))</x:f>
+      <x:c r="N35" s="131" t="n">
+        <x:v>4712400</x:v>
+      </x:c>
+      <x:c r="O35" s="167"/>
+      <x:c r="P35" s="131" t="n">
+        <x:f>IF(G35=0,0,CEILING(MAX(100,10*G35),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q35" s="30"/>
-      <x:c r="R35" s="29" t="n">
-        <x:f>IF(Q35="",P35,MAX(P35,Q35))</x:f>
+      <x:c r="Q35" s="178"/>
+      <x:c r="R35" s="131" t="n">
+        <x:f>IF(Q35="",P35,CEILING(MAX(P35,Q35),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S35" s="31" t="n">
+      <x:c r="S35" s="168" t="n">
         <x:f>IF(ISNUMBER(H35),R35*H35,"")</x:f>
-        <x:v>2.9000000000000004</x:v>
-      </x:c>
-      <x:c r="T35" s="26" t="str">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="T35" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U35" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W35" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X35" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y35" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="27" hidden="0" customHeight="1">
-      <x:c r="A36" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B36" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="E36" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F36" s="17" t="n">
+      <x:c r="U35" s="142" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17415. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V35" s="142"/>
+      <x:c r="W35" s="142" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X35" s="192" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y35" s="142" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17415.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="28" hidden="0" customHeight="1">
+      <x:c r="A36" s="179" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B36" s="179" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C36" s="179" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D36" s="179" t="str">
+        <x:v>0805W8F4701T5E</x:v>
+      </x:c>
+      <x:c r="E36" s="169" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F36" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G36" s="17" t="n">
+      <x:c r="G36" s="170" t="n">
         <x:f aca="0">F36*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H36" s="18" t="n">
-        <x:f aca="0">IF(R36&gt;=1000,0.00973,IF(R36&gt;=500,0.01136,IF(R36&gt;=250,0.01344,IF(R36&gt;=100,0.0171,IF(R36&gt;=50,0.0208,IF(R36&gt;=25,0.0256,IF(R36&gt;=10,0.034,0.1)))))))</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="I36" s="19" t="n">
+      <x:c r="H36" s="171" t="n">
+        <x:f aca="0">IF(R36&gt;=100000,0.0029,IF(R36&gt;=50000,0.003,IF(R36&gt;=10000,0.0032,IF(R36&gt;=5000,0.0035,IF(R36&gt;=1000,0.004,0.0051)))))</x:f>
+        <x:v>0.0051</x:v>
+      </x:c>
+      <x:c r="I36" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H36),F36*H36,"")</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="J36" s="19" t="n">
+        <x:v>0.0051</x:v>
+      </x:c>
+      <x:c r="J36" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H36),G36*H36,"")</x:f>
-        <x:v>0.0855</x:v>
-      </x:c>
-      <x:c r="K36" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L36" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M36" s="16" t="str">
+        <x:v>0.025500000000000002</x:v>
+      </x:c>
+      <x:c r="K36" s="169" t="str">
+        <x:v>LCSC C17673</x:v>
+      </x:c>
+      <x:c r="L36" s="169" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M36" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N36),IF(N36&lt;R36,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N36" s="40" t="n">
-        <x:v>724039</x:v>
-      </x:c>
-      <x:c r="P36" s="29" t="n">
-        <x:f>IF(G36=0,0,MAX(100,10*G36))</x:f>
+      <x:c r="N36" s="170" t="n">
+        <x:v>1678600</x:v>
+      </x:c>
+      <x:c r="O36" s="167"/>
+      <x:c r="P36" s="170" t="n">
+        <x:f>IF(G36=0,0,CEILING(MAX(100,10*G36),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q36" s="30"/>
-      <x:c r="R36" s="29" t="n">
-        <x:f>IF(Q36="",P36,MAX(P36,Q36))</x:f>
+      <x:c r="Q36" s="178"/>
+      <x:c r="R36" s="170" t="n">
+        <x:f>IF(Q36="",P36,CEILING(MAX(P36,Q36),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S36" s="31" t="n">
+      <x:c r="S36" s="177" t="n">
         <x:f>IF(ISNUMBER(H36),R36*H36,"")</x:f>
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="T36" s="26" t="str">
+        <x:v>0.51</x:v>
+      </x:c>
+      <x:c r="T36" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U36" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W36" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X36" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y36" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="27" hidden="0" customHeight="1">
-      <x:c r="A37" s="10" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B37" s="10" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C37" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D37" s="10" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
+      <x:c r="U36" s="175" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17673. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V36" s="142"/>
+      <x:c r="W36" s="175" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X36" s="191" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y36" s="175" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17673.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="28" hidden="0" customHeight="1">
+      <x:c r="A37" s="130" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B37" s="130" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C37" s="130" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D37" s="130" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E37" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F37" s="11" t="n">
+      <x:c r="F37" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G37" s="11" t="n">
+      <x:c r="G37" s="131" t="n">
         <x:f aca="0">F37*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H37" s="12" t="n">
+      <x:c r="H37" s="132" t="n">
         <x:f aca="0">IF(R37&gt;=1000,0.00973,IF(R37&gt;=500,0.01136,IF(R37&gt;=250,0.01344,IF(R37&gt;=100,0.0171,IF(R37&gt;=50,0.0208,IF(R37&gt;=25,0.0256,IF(R37&gt;=10,0.034,0.1)))))))</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="I37" s="13" t="n">
+      <x:c r="I37" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H37),F37*H37,"")</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="J37" s="13" t="n">
+      <x:c r="J37" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H37),G37*H37,"")</x:f>
         <x:v>0.0855</x:v>
       </x:c>
-      <x:c r="K37" s="14" t="s">
+      <x:c r="K37" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L37" s="1" t="s">
+      <x:c r="L37" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M37" s="1" t="str">
+      <x:c r="M37" s="130" t="str">
         <x:f>IF(ISNUMBER(N37),IF(N37&lt;R37,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N37" s="39" t="n">
+      <x:c r="N37" s="131" t="n">
         <x:v>37932</x:v>
       </x:c>
-      <x:c r="P37" s="29" t="n">
+      <x:c r="O37" s="167"/>
+      <x:c r="P37" s="131" t="n">
         <x:f>IF(G37=0,0,MAX(100,10*G37))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q37" s="30"/>
-      <x:c r="R37" s="29" t="n">
+      <x:c r="Q37" s="178"/>
+      <x:c r="R37" s="131" t="n">
         <x:f>IF(Q37="",P37,MAX(P37,Q37))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S37" s="31" t="n">
+      <x:c r="S37" s="168" t="n">
         <x:f>IF(ISNUMBER(H37),R37*H37,"")</x:f>
         <x:v>1.71</x:v>
       </x:c>
-      <x:c r="T37" s="26" t="str">
+      <x:c r="T37" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U37" s="27" t="str">
+      <x:c r="U37" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W37" s="27" t="str">
+      <x:c r="V37" s="142"/>
+      <x:c r="W37" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X37" s="38" t="d">
+      <x:c r="X37" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y37" s="27" t="str">
+      <x:c r="Y37" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="27" hidden="0" customHeight="1">
-      <x:c r="A38" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B38" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E38" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F38" s="17" t="n">
+    <x:row r="38" ht="28" hidden="0" customHeight="1">
+      <x:c r="A38" s="179" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B38" s="179" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C38" s="179" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D38" s="179" t="str">
+        <x:v>0805W8F1001T5E</x:v>
+      </x:c>
+      <x:c r="E38" s="169" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F38" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G38" s="17" t="n">
+      <x:c r="G38" s="170" t="n">
         <x:f aca="0">F38*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H38" s="18" t="n">
-        <x:f aca="0">IF(R38&gt;=1000,0.00973,IF(R38&gt;=500,0.01136,IF(R38&gt;=250,0.01344,IF(R38&gt;=100,0.0171,IF(R38&gt;=50,0.0208,IF(R38&gt;=25,0.0256,IF(R38&gt;=10,0.034,0.1)))))))</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="I38" s="19" t="n">
+      <x:c r="H38" s="171" t="n">
+        <x:f aca="0">IF(R38&gt;=50000,0.0022,IF(R38&gt;=10000,0.0024,IF(R38&gt;=5000,0.0026,IF(R38&gt;=1000,0.0032,0.0041))))</x:f>
+        <x:v>0.0041</x:v>
+      </x:c>
+      <x:c r="I38" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H38),F38*H38,"")</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="J38" s="19" t="n">
+        <x:v>0.0041</x:v>
+      </x:c>
+      <x:c r="J38" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H38),G38*H38,"")</x:f>
-        <x:v>0.0855</x:v>
-      </x:c>
-      <x:c r="K38" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L38" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M38" s="16" t="str">
+        <x:v>0.0205</x:v>
+      </x:c>
+      <x:c r="K38" s="169" t="str">
+        <x:v>LCSC C17513</x:v>
+      </x:c>
+      <x:c r="L38" s="169" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M38" s="179" t="str">
         <x:f>IF(ISNUMBER(N38),IF(N38&lt;R38,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N38" s="40" t="n">
-        <x:v>832298</x:v>
-      </x:c>
-      <x:c r="P38" s="29" t="n">
-        <x:f>IF(G38=0,0,MAX(100,10*G38))</x:f>
+      <x:c r="N38" s="170" t="n">
+        <x:v>24259800</x:v>
+      </x:c>
+      <x:c r="O38" s="167"/>
+      <x:c r="P38" s="170" t="n">
+        <x:f>IF(G38=0,0,CEILING(MAX(100,10*G38),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q38" s="30"/>
-      <x:c r="R38" s="29" t="n">
-        <x:f>IF(Q38="",P38,MAX(P38,Q38))</x:f>
+      <x:c r="Q38" s="178"/>
+      <x:c r="R38" s="170" t="n">
+        <x:f>IF(Q38="",P38,CEILING(MAX(P38,Q38),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S38" s="31" t="n">
+      <x:c r="S38" s="177" t="n">
         <x:f>IF(ISNUMBER(H38),R38*H38,"")</x:f>
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="T38" s="26" t="str">
+        <x:v>0.41000000000000003</x:v>
+      </x:c>
+      <x:c r="T38" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U38" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W38" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X38" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y38" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="27" hidden="0" customHeight="1">
-      <x:c r="A39" s="10" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B39" s="10" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C39" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D39" s="10" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
+      <x:c r="U38" s="175" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17513. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V38" s="142"/>
+      <x:c r="W38" s="175" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X38" s="191" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y38" s="175" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17513.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="28" hidden="0" customHeight="1">
+      <x:c r="A39" s="130" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B39" s="130" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C39" s="130" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D39" s="130" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E39" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="n">
+      <x:c r="F39" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G39" s="11" t="n">
+      <x:c r="G39" s="131" t="n">
         <x:f aca="0">F39*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H39" s="12" t="n">
+      <x:c r="H39" s="132" t="n">
         <x:f aca="0">IF(R39&gt;=1000,0.00973,IF(R39&gt;=500,0.01136,IF(R39&gt;=250,0.01344,IF(R39&gt;=100,0.0171,IF(R39&gt;=50,0.0208,IF(R39&gt;=25,0.0256,IF(R39&gt;=10,0.034,0.1)))))))</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="I39" s="13" t="n">
+      <x:c r="I39" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H39),F39*H39,"")</x:f>
         <x:v>0.0171</x:v>
       </x:c>
-      <x:c r="J39" s="13" t="n">
+      <x:c r="J39" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H39),G39*H39,"")</x:f>
         <x:v>0.0855</x:v>
       </x:c>
-      <x:c r="K39" s="14" t="s">
+      <x:c r="K39" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L39" s="1" t="s">
+      <x:c r="L39" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M39" s="1" t="str">
+      <x:c r="M39" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N39),IF(N39&lt;R39,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N39" s="39" t="n">
+      <x:c r="N39" s="131" t="n">
         <x:v>38077</x:v>
       </x:c>
-      <x:c r="P39" s="29" t="n">
+      <x:c r="O39" s="167"/>
+      <x:c r="P39" s="131" t="n">
         <x:f>IF(G39=0,0,MAX(100,10*G39))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q39" s="30"/>
-      <x:c r="R39" s="29" t="n">
+      <x:c r="Q39" s="178"/>
+      <x:c r="R39" s="131" t="n">
         <x:f>IF(Q39="",P39,MAX(P39,Q39))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S39" s="31" t="n">
+      <x:c r="S39" s="168" t="n">
         <x:f>IF(ISNUMBER(H39),R39*H39,"")</x:f>
         <x:v>1.71</x:v>
       </x:c>
-      <x:c r="T39" s="26" t="str">
+      <x:c r="T39" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U39" s="27" t="str">
+      <x:c r="U39" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W39" s="27" t="str">
+      <x:c r="V39" s="142"/>
+      <x:c r="W39" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X39" s="38" t="d">
+      <x:c r="X39" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y39" s="27" t="str">
+      <x:c r="Y39" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="27" hidden="0" customHeight="1">
-      <x:c r="A40" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B40" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E40" s="16" t="s">
+    <x:row r="40" ht="28" hidden="0" customHeight="1">
+      <x:c r="A40" s="179" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B40" s="179" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C40" s="179" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D40" s="179" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E40" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F40" s="17" t="n">
+      <x:c r="F40" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G40" s="17" t="n">
+      <x:c r="G40" s="170" t="n">
         <x:f aca="0">F40*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H40" s="18" t="n">
+      <x:c r="H40" s="171" t="n">
         <x:f aca="0">IF(R40&gt;=1000,0.03376,IF(R40&gt;=500,0.0377,IF(R40&gt;=250,0.04268,IF(R40&gt;=100,0.0514,IF(R40&gt;=50,0.06,IF(R40&gt;=25,0.0712,IF(R40&gt;=10,0.09,0.18)))))))</x:f>
         <x:v>0.0514</x:v>
       </x:c>
-      <x:c r="I40" s="19" t="n">
+      <x:c r="I40" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H40),F40*H40,"")</x:f>
         <x:v>0.0514</x:v>
       </x:c>
-      <x:c r="J40" s="19" t="n">
+      <x:c r="J40" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H40),G40*H40,"")</x:f>
         <x:v>0.257</x:v>
       </x:c>
-      <x:c r="K40" s="20" t="s">
+      <x:c r="K40" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L40" s="16" t="s">
+      <x:c r="L40" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M40" s="16" t="str">
+      <x:c r="M40" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N40),IF(N40&lt;R40,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N40" s="40" t="n">
+      <x:c r="N40" s="170" t="n">
         <x:v>15988</x:v>
       </x:c>
-      <x:c r="P40" s="29" t="n">
+      <x:c r="O40" s="167"/>
+      <x:c r="P40" s="170" t="n">
         <x:f>IF(G40=0,0,MAX(100,10*G40))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q40" s="30"/>
-      <x:c r="R40" s="29" t="n">
+      <x:c r="Q40" s="178"/>
+      <x:c r="R40" s="170" t="n">
         <x:f>IF(Q40="",P40,MAX(P40,Q40))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S40" s="31" t="n">
+      <x:c r="S40" s="177" t="n">
         <x:f>IF(ISNUMBER(H40),R40*H40,"")</x:f>
         <x:v>5.140000000000001</x:v>
       </x:c>
-      <x:c r="T40" s="26" t="str">
+      <x:c r="T40" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U40" s="27" t="str">
+      <x:c r="U40" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W40" s="27" t="str">
+      <x:c r="V40" s="142"/>
+      <x:c r="W40" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X40" s="38" t="d">
+      <x:c r="X40" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y40" s="27" t="str">
+      <x:c r="Y40" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="27" hidden="0" customHeight="1">
-      <x:c r="A41" s="10" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B41" s="10" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C41" s="10" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D41" s="10" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F41" s="11" t="n">
+    <x:row r="41" ht="28" hidden="0" customHeight="1">
+      <x:c r="A41" s="130" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B41" s="130" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C41" s="130" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D41" s="130" t="str">
+        <x:v>0805W8F1002T5E</x:v>
+      </x:c>
+      <x:c r="E41" s="122" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F41" s="131" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G41" s="11" t="n">
+      <x:c r="G41" s="131" t="n">
         <x:f aca="0">F41*$B$4</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H41" s="12" t="n">
-        <x:f aca="0">IF(R41&gt;=100,0.0171,IF(R41&gt;=50,0.0208,IF(R41&gt;=25,0.0256,IF(R41&gt;=10,0.034,0.1))))</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="I41" s="13" t="n">
+      <x:c r="H41" s="132" t="n">
+        <x:f aca="0">IF(R41&gt;=50000,0.0014,IF(R41&gt;=10000,0.0016,IF(R41&gt;=5000,0.0018,IF(R41&gt;=1000,0.0026,0.0034))))</x:f>
+        <x:v>0.0034</x:v>
+      </x:c>
+      <x:c r="I41" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H41),F41*H41,"")</x:f>
-        <x:v>0.0342</x:v>
-      </x:c>
-      <x:c r="J41" s="13" t="n">
+        <x:v>0.0068</x:v>
+      </x:c>
+      <x:c r="J41" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H41),G41*H41,"")</x:f>
-        <x:v>0.171</x:v>
-      </x:c>
-      <x:c r="K41" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L41" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M41" s="1" t="str">
+        <x:v>0.033999999999999996</x:v>
+      </x:c>
+      <x:c r="K41" s="122" t="str">
+        <x:v>LCSC C17414</x:v>
+      </x:c>
+      <x:c r="L41" s="122" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M41" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N41),IF(N41&lt;R41,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N41" s="39" t="n">
-        <x:v>1523983</x:v>
-      </x:c>
-      <x:c r="P41" s="29" t="n">
-        <x:f>IF(G41=0,0,MAX(100,10*G41))</x:f>
+      <x:c r="N41" s="131" t="n">
+        <x:v>48598900</x:v>
+      </x:c>
+      <x:c r="O41" s="167"/>
+      <x:c r="P41" s="131" t="n">
+        <x:f>IF(G41=0,0,CEILING(MAX(100,10*G41),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q41" s="30"/>
-      <x:c r="R41" s="29" t="n">
-        <x:f>IF(Q41="",P41,MAX(P41,Q41))</x:f>
+      <x:c r="Q41" s="178"/>
+      <x:c r="R41" s="131" t="n">
+        <x:f>IF(Q41="",P41,CEILING(MAX(P41,Q41),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S41" s="31" t="n">
+      <x:c r="S41" s="168" t="n">
         <x:f>IF(ISNUMBER(H41),R41*H41,"")</x:f>
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="T41" s="26" t="str">
+        <x:v>0.33999999999999997</x:v>
+      </x:c>
+      <x:c r="T41" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U41" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W41" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X41" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y41" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="27" hidden="0" customHeight="1">
-      <x:c r="A42" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B42" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D42" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="E42" s="16" t="s">
+      <x:c r="U41" s="142" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17414. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V41" s="142"/>
+      <x:c r="W41" s="142" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X41" s="192" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y41" s="142" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17414.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="28" hidden="0" customHeight="1">
+      <x:c r="A42" s="179" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B42" s="179" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C42" s="179" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D42" s="179" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E42" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F42" s="17" t="n">
+      <x:c r="F42" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G42" s="17" t="n">
+      <x:c r="G42" s="170" t="n">
         <x:f aca="0">F42*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H42" s="18" t="n">
+      <x:c r="H42" s="171" t="n">
         <x:f aca="0">IF(R42&gt;=1000,0.26458,IF(R42&gt;=500,0.27926,IF(R42&gt;=250,0.29772,IF(R42&gt;=100,0.3296,IF(R42&gt;=50,0.361,IF(R42&gt;=25,0.4008,IF(R42&gt;=10,0.47,0.78)))))))</x:f>
         <x:v>0.3296</x:v>
       </x:c>
-      <x:c r="I42" s="19" t="n">
+      <x:c r="I42" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H42),F42*H42,"")</x:f>
         <x:v>0.3296</x:v>
       </x:c>
-      <x:c r="J42" s="19" t="n">
+      <x:c r="J42" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H42),G42*H42,"")</x:f>
         <x:v>1.6480000000000001</x:v>
       </x:c>
-      <x:c r="K42" s="20" t="s">
+      <x:c r="K42" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L42" s="16" t="s">
+      <x:c r="L42" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M42" s="16" t="str">
+      <x:c r="M42" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N42),IF(N42&lt;R42,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N42" s="40" t="n">
+      <x:c r="N42" s="170" t="n">
         <x:v>8500</x:v>
       </x:c>
-      <x:c r="P42" s="29" t="n">
+      <x:c r="O42" s="167"/>
+      <x:c r="P42" s="170" t="n">
         <x:f>IF(G42=0,0,MAX(100,10*G42))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q42" s="30"/>
-      <x:c r="R42" s="29" t="n">
+      <x:c r="Q42" s="178"/>
+      <x:c r="R42" s="170" t="n">
         <x:f>IF(Q42="",P42,MAX(P42,Q42))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S42" s="31" t="n">
+      <x:c r="S42" s="177" t="n">
         <x:f>IF(ISNUMBER(H42),R42*H42,"")</x:f>
         <x:v>32.96</x:v>
       </x:c>
-      <x:c r="T42" s="26" t="str">
+      <x:c r="T42" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U42" s="27" t="str">
+      <x:c r="U42" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W42" s="27" t="str">
+      <x:c r="V42" s="142"/>
+      <x:c r="W42" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X42" s="38" t="d">
+      <x:c r="X42" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y42" s="27" t="str">
+      <x:c r="Y42" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="27" hidden="0" customHeight="1">
-      <x:c r="A43" s="10" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B43" s="10" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C43" s="10" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D43" s="10" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
+    <x:row r="43" ht="28" hidden="0" customHeight="1">
+      <x:c r="A43" s="130" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B43" s="130" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C43" s="130" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D43" s="130" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E43" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F43" s="11" t="n">
+      <x:c r="F43" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G43" s="11" t="n">
+      <x:c r="G43" s="131" t="n">
         <x:f aca="0">F43*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H43" s="12" t="n">
+      <x:c r="H43" s="132" t="n">
         <x:f aca="0">IF(R43&gt;=1000,0.35468,IF(R43&gt;=500,0.37218,IF(R43&gt;=250,0.3942,IF(R43&gt;=100,0.4322,IF(R43&gt;=50,0.4698,IF(R43&gt;=25,0.5168,IF(R43&gt;=10,0.599,0.96)))))))</x:f>
         <x:v>0.4322</x:v>
       </x:c>
-      <x:c r="I43" s="13" t="n">
+      <x:c r="I43" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H43),F43*H43,"")</x:f>
         <x:v>0.4322</x:v>
       </x:c>
-      <x:c r="J43" s="13" t="n">
+      <x:c r="J43" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H43),G43*H43,"")</x:f>
         <x:v>2.161</x:v>
       </x:c>
-      <x:c r="K43" s="14" t="s">
+      <x:c r="K43" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L43" s="1" t="s">
+      <x:c r="L43" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M43" s="1" t="str">
+      <x:c r="M43" s="130" t="str">
         <x:f>IF(ISNUMBER(N43),IF(N43&lt;R43,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N43" s="39" t="n">
+      <x:c r="N43" s="131" t="n">
         <x:v>14703</x:v>
       </x:c>
-      <x:c r="P43" s="29" t="n">
+      <x:c r="O43" s="167"/>
+      <x:c r="P43" s="131" t="n">
         <x:f>IF(G43=0,0,MAX(100,10*G43))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q43" s="30"/>
-      <x:c r="R43" s="29" t="n">
+      <x:c r="Q43" s="178"/>
+      <x:c r="R43" s="131" t="n">
         <x:f>IF(Q43="",P43,MAX(P43,Q43))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S43" s="31" t="n">
+      <x:c r="S43" s="168" t="n">
         <x:f>IF(ISNUMBER(H43),R43*H43,"")</x:f>
         <x:v>43.22</x:v>
       </x:c>
-      <x:c r="T43" s="26" t="str">
+      <x:c r="T43" s="142" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U43" s="27" t="str">
+      <x:c r="U43" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W43" s="27" t="str">
+      <x:c r="V43" s="142"/>
+      <x:c r="W43" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X43" s="38" t="d">
+      <x:c r="X43" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y43" s="27" t="str">
+      <x:c r="Y43" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="27" hidden="0" customHeight="1">
-      <x:c r="A44" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B44" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C44" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D44" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="E44" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F44" s="17" t="n">
+    <x:row r="44" ht="28" hidden="0" customHeight="1">
+      <x:c r="A44" s="179" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B44" s="179" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C44" s="179" t="str">
+        <x:v>UNI-ROYAL</x:v>
+      </x:c>
+      <x:c r="D44" s="179" t="str">
+        <x:v>0805W8F1000T5E</x:v>
+      </x:c>
+      <x:c r="E44" s="169" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="F44" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G44" s="17" t="n">
+      <x:c r="G44" s="170" t="n">
         <x:f aca="0">F44*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H44" s="18" t="n">
-        <x:f aca="0">IF(R44&gt;=1000,0.00973,IF(R44&gt;=500,0.01136,IF(R44&gt;=250,0.01344,IF(R44&gt;=100,0.0171,IF(R44&gt;=50,0.0208,IF(R44&gt;=25,0.0256,IF(R44&gt;=10,0.034,0.1)))))))</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="I44" s="19" t="n">
+      <x:c r="H44" s="171" t="n">
+        <x:f aca="0">IF(R44&gt;=50000,0.0023,IF(R44&gt;=10000,0.0025,IF(R44&gt;=5000,0.0028,IF(R44&gt;=1000,0.0033,0.0043))))</x:f>
+        <x:v>0.0043</x:v>
+      </x:c>
+      <x:c r="I44" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H44),F44*H44,"")</x:f>
-        <x:v>0.0171</x:v>
-      </x:c>
-      <x:c r="J44" s="19" t="n">
+        <x:v>0.0043</x:v>
+      </x:c>
+      <x:c r="J44" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H44),G44*H44,"")</x:f>
-        <x:v>0.0855</x:v>
-      </x:c>
-      <x:c r="K44" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L44" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M44" s="16" t="str">
+        <x:v>0.0215</x:v>
+      </x:c>
+      <x:c r="K44" s="169" t="str">
+        <x:v>LCSC C17408</x:v>
+      </x:c>
+      <x:c r="L44" s="169" t="str">
+        <x:v>Catalog 10/08/26</x:v>
+      </x:c>
+      <x:c r="M44" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N44),IF(N44&lt;R44,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N44" s="40" t="n">
-        <x:v>1312828</x:v>
-      </x:c>
-      <x:c r="P44" s="29" t="n">
-        <x:f>IF(G44=0,0,MAX(100,10*G44))</x:f>
+      <x:c r="N44" s="170" t="n">
+        <x:v>6871100</x:v>
+      </x:c>
+      <x:c r="O44" s="167"/>
+      <x:c r="P44" s="170" t="n">
+        <x:f>IF(G44=0,0,CEILING(MAX(100,10*G44),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="Q44" s="30"/>
-      <x:c r="R44" s="29" t="n">
-        <x:f>IF(Q44="",P44,MAX(P44,Q44))</x:f>
+      <x:c r="Q44" s="178"/>
+      <x:c r="R44" s="170" t="n">
+        <x:f>IF(Q44="",P44,CEILING(MAX(P44,Q44),100))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="S44" s="31" t="n">
+      <x:c r="S44" s="177" t="n">
         <x:f>IF(ISNUMBER(H44),R44*H44,"")</x:f>
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="T44" s="26" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="T44" s="175" t="str">
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
-      <x:c r="U44" s="27" t="str">
-        <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
-      </x:c>
-      <x:c r="W44" s="27" t="str">
-        <x:v>Repaired; page verified</x:v>
-      </x:c>
-      <x:c r="X44" s="38" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="Y44" s="27" t="str">
-        <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="27" hidden="0" customHeight="1">
-      <x:c r="A45" s="10" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B45" s="10" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C45" s="10" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D45" s="10" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
+      <x:c r="U44" s="175" t="str">
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17408. Buy one lot per MPN.</x:v>
+      </x:c>
+      <x:c r="V44" s="142"/>
+      <x:c r="W44" s="175" t="str">
+        <x:v>Exact MPN checked</x:v>
+      </x:c>
+      <x:c r="X44" s="191" t="n">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="Y44" s="175" t="str">
+        <x:v>Reported stock snapshot. Confirm stock and JLC assembly availability at order time. https://www.lcsc.com/product-detail/C17408.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="28" hidden="0" customHeight="1">
+      <x:c r="A45" s="130" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B45" s="130" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C45" s="130" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D45" s="130" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E45" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F45" s="11" t="n">
+      <x:c r="F45" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G45" s="11" t="n">
+      <x:c r="G45" s="131" t="n">
         <x:f aca="0">F45*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H45" s="12" t="n">
+      <x:c r="H45" s="132" t="n">
         <x:f aca="0">IF(R45&gt;=250,6.65552,IF(R45&gt;=100,6.7577,IF(R45&gt;=25,7.3728,IF(R45&gt;=10,7.933,10.17))))</x:f>
         <x:v>10.17</x:v>
       </x:c>
-      <x:c r="I45" s="13" t="n">
+      <x:c r="I45" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H45),F45*H45,"")</x:f>
         <x:v>10.17</x:v>
       </x:c>
-      <x:c r="J45" s="13" t="n">
+      <x:c r="J45" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H45),G45*H45,"")</x:f>
         <x:v>50.85</x:v>
       </x:c>
-      <x:c r="K45" s="14" t="s">
+      <x:c r="K45" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L45" s="1" t="s">
+      <x:c r="L45" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M45" s="1" t="str">
+      <x:c r="M45" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N45),IF(N45&lt;R45,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Short stock</x:v>
       </x:c>
-      <x:c r="N45" s="39" t="n">
+      <x:c r="N45" s="131" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P45" s="29" t="n">
+      <x:c r="O45" s="167"/>
+      <x:c r="P45" s="131" t="n">
         <x:f>ROUNDUP(G45*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q45" s="30"/>
-      <x:c r="R45" s="29" t="n">
+      <x:c r="Q45" s="178"/>
+      <x:c r="R45" s="131" t="n">
         <x:f>IF(Q45="",P45,MAX(P45,Q45))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S45" s="31" t="n">
+      <x:c r="S45" s="168" t="n">
         <x:f>IF(ISNUMBER(H45),R45*H45,"")</x:f>
         <x:v>61.019999999999996</x:v>
       </x:c>
-      <x:c r="T45" s="26" t="str">
+      <x:c r="T45" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U45" s="27" t="str">
+      <x:c r="U45" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W45" s="27" t="str">
+      <x:c r="V45" s="142"/>
+      <x:c r="W45" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X45" s="38" t="d">
+      <x:c r="X45" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y45" s="27" t="str">
+      <x:c r="Y45" s="142" t="str">
         <x:v>Supplier expects 2,500 on Oct 13, 2026. Expected arrivals are estimates.</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="27" hidden="0" customHeight="1">
-      <x:c r="A46" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="B46" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C46" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D46" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="E46" s="16" t="s">
+    <x:row r="46" ht="28" hidden="0" customHeight="1">
+      <x:c r="A46" s="179" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B46" s="179" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C46" s="179" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D46" s="179" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E46" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F46" s="17" t="n">
+      <x:c r="F46" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G46" s="17" t="n">
+      <x:c r="G46" s="170" t="n">
         <x:f aca="0">F46*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H46" s="18" t="n">
+      <x:c r="H46" s="171" t="n">
         <x:v>4.68</x:v>
       </x:c>
-      <x:c r="I46" s="19" t="n">
+      <x:c r="I46" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H46),F46*H46,"")</x:f>
         <x:v>4.68</x:v>
       </x:c>
-      <x:c r="J46" s="19" t="n">
+      <x:c r="J46" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H46),G46*H46,"")</x:f>
         <x:v>23.4</x:v>
       </x:c>
-      <x:c r="K46" s="20" t="s">
+      <x:c r="K46" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L46" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="M46" s="16" t="str">
+      <x:c r="L46" s="169" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M46" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N46),IF(N46&lt;R46,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Short stock</x:v>
       </x:c>
-      <x:c r="N46" s="40" t="n">
+      <x:c r="N46" s="170" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P46" s="29" t="n">
+      <x:c r="O46" s="167"/>
+      <x:c r="P46" s="170" t="n">
         <x:f>ROUNDUP(G46*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q46" s="30"/>
-      <x:c r="R46" s="29" t="n">
+      <x:c r="Q46" s="178"/>
+      <x:c r="R46" s="170" t="n">
         <x:f>IF(Q46="",P46,MAX(P46,Q46))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S46" s="31" t="n">
+      <x:c r="S46" s="177" t="n">
         <x:f>IF(ISNUMBER(H46),R46*H46,"")</x:f>
         <x:v>28.08</x:v>
       </x:c>
-      <x:c r="T46" s="26" t="str">
+      <x:c r="T46" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U46" s="27" t="str">
+      <x:c r="U46" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W46" s="27" t="str">
+      <x:c r="V46" s="142"/>
+      <x:c r="W46" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X46" s="38" t="d">
+      <x:c r="X46" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y46" s="27" t="str">
+      <x:c r="Y46" s="175" t="str">
         <x:v>Supplier expects 1,903 on Jan 4 and 597 on Jan 7, 2027. Expected arrivals are estimates.</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="27" hidden="0" customHeight="1">
-      <x:c r="A47" s="10" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="B47" s="10" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="C47" s="10" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D47" s="10" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
+    <x:row r="47" ht="28" hidden="0" customHeight="1">
+      <x:c r="A47" s="130" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B47" s="130" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C47" s="130" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D47" s="130" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E47" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F47" s="11" t="n">
+      <x:c r="F47" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G47" s="11" t="n">
+      <x:c r="G47" s="131" t="n">
         <x:f aca="0">F47*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H47" s="12" t="n">
+      <x:c r="H47" s="132" t="n">
         <x:f aca="0">IF(R47&gt;=250,4.02392,IF(R47&gt;=100,4.1691,IF(R47&gt;=25,4.5808,IF(R47&gt;=10,4.955,6.45))))</x:f>
         <x:v>6.45</x:v>
       </x:c>
-      <x:c r="I47" s="13" t="n">
+      <x:c r="I47" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H47),F47*H47,"")</x:f>
         <x:v>6.45</x:v>
       </x:c>
-      <x:c r="J47" s="13" t="n">
+      <x:c r="J47" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H47),G47*H47,"")</x:f>
         <x:v>32.25</x:v>
       </x:c>
-      <x:c r="K47" s="14" t="s">
+      <x:c r="K47" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L47" s="1" t="s">
+      <x:c r="L47" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M47" s="1" t="str">
+      <x:c r="M47" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N47),IF(N47&lt;R47,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N47" s="39" t="n">
+      <x:c r="N47" s="131" t="n">
         <x:v>1663</x:v>
       </x:c>
-      <x:c r="P47" s="29" t="n">
+      <x:c r="O47" s="167"/>
+      <x:c r="P47" s="131" t="n">
         <x:f>ROUNDUP(G47*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q47" s="30"/>
-      <x:c r="R47" s="29" t="n">
+      <x:c r="Q47" s="178"/>
+      <x:c r="R47" s="131" t="n">
         <x:f>IF(Q47="",P47,MAX(P47,Q47))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S47" s="31" t="n">
+      <x:c r="S47" s="168" t="n">
         <x:f>IF(ISNUMBER(H47),R47*H47,"")</x:f>
         <x:v>38.7</x:v>
       </x:c>
-      <x:c r="T47" s="26" t="str">
+      <x:c r="T47" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U47" s="27" t="str">
+      <x:c r="U47" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W47" s="27" t="str">
+      <x:c r="V47" s="142"/>
+      <x:c r="W47" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X47" s="38" t="d">
+      <x:c r="X47" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y47" s="27" t="str">
+      <x:c r="Y47" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="27" hidden="0" customHeight="1">
-      <x:c r="A48" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="B48" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C48" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D48" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E48" s="16" t="s">
+    <x:row r="48" ht="28" hidden="0" customHeight="1">
+      <x:c r="A48" s="179" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B48" s="179" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C48" s="179" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D48" s="179" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E48" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F48" s="17" t="n">
+      <x:c r="F48" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G48" s="17" t="n">
+      <x:c r="G48" s="170" t="n">
         <x:f aca="0">F48*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H48" s="18" t="n">
+      <x:c r="H48" s="171" t="n">
         <x:f aca="0">IF(R48&gt;=1000,0.07973,IF(R48&gt;=500,0.08374,IF(R48&gt;=250,0.0886,IF(R48&gt;=100,0.0967,IF(R48&gt;=25,0.1136,IF(R48&gt;=10,0.129,0.19))))))</x:f>
         <x:v>0.19</x:v>
       </x:c>
-      <x:c r="I48" s="19" t="n">
+      <x:c r="I48" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H48),F48*H48,"")</x:f>
         <x:v>0.19</x:v>
       </x:c>
-      <x:c r="J48" s="19" t="n">
+      <x:c r="J48" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H48),G48*H48,"")</x:f>
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="K48" s="20" t="s">
+      <x:c r="K48" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L48" s="16" t="s">
+      <x:c r="L48" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M48" s="16" t="str">
+      <x:c r="M48" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N48),IF(N48&lt;R48,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N48" s="40" t="n">
+      <x:c r="N48" s="170" t="n">
         <x:v>10686</x:v>
       </x:c>
-      <x:c r="P48" s="29" t="n">
+      <x:c r="O48" s="167"/>
+      <x:c r="P48" s="170" t="n">
         <x:f>ROUNDUP(G48*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q48" s="30"/>
-      <x:c r="R48" s="29" t="n">
+      <x:c r="Q48" s="178"/>
+      <x:c r="R48" s="170" t="n">
         <x:f>IF(Q48="",P48,MAX(P48,Q48))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S48" s="31" t="n">
+      <x:c r="S48" s="177" t="n">
         <x:f>IF(ISNUMBER(H48),R48*H48,"")</x:f>
         <x:v>1.1400000000000001</x:v>
       </x:c>
-      <x:c r="T48" s="26" t="str">
+      <x:c r="T48" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U48" s="27" t="str">
+      <x:c r="U48" s="175" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W48" s="27" t="str">
+      <x:c r="V48" s="142"/>
+      <x:c r="W48" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X48" s="38" t="d">
+      <x:c r="X48" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y48" s="27" t="str">
+      <x:c r="Y48" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="27" hidden="0" customHeight="1">
-      <x:c r="A49" s="10" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="B49" s="10" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C49" s="10" t="s">
+    <x:row r="49" ht="28" hidden="0" customHeight="1">
+      <x:c r="A49" s="130" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D49" s="10" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
+      <x:c r="B49" s="130" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C49" s="130" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D49" s="130" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E49" s="122" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F49" s="11" t="n">
+      <x:c r="F49" s="131" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G49" s="11" t="n">
+      <x:c r="G49" s="131" t="n">
         <x:f aca="0">F49*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H49" s="12" t="n">
+      <x:c r="H49" s="132" t="n">
         <x:f aca="0">IF(R49&gt;=250,6.1812,IF(R49&gt;=100,6.2941,IF(R49&gt;=25,6.874,IF(R49&gt;=10,7.402,9.51))))</x:f>
         <x:v>9.51</x:v>
       </x:c>
-      <x:c r="I49" s="13" t="n">
+      <x:c r="I49" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H49),F49*H49,"")</x:f>
         <x:v>9.51</x:v>
       </x:c>
-      <x:c r="J49" s="13" t="n">
+      <x:c r="J49" s="133" t="n">
         <x:f aca="0">IF(ISNUMBER(H49),G49*H49,"")</x:f>
         <x:v>47.55</x:v>
       </x:c>
-      <x:c r="K49" s="14" t="s">
+      <x:c r="K49" s="122" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L49" s="1" t="s">
+      <x:c r="L49" s="122" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M49" s="1" t="str">
+      <x:c r="M49" s="130" t="str">
         <x:f aca="0">IF(ISNUMBER(N49),IF(N49&lt;R49,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N49" s="39" t="n">
+      <x:c r="N49" s="131" t="n">
         <x:v>6425</x:v>
       </x:c>
-      <x:c r="P49" s="29" t="n">
+      <x:c r="O49" s="167"/>
+      <x:c r="P49" s="131" t="n">
         <x:f>ROUNDUP(G49*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q49" s="30"/>
-      <x:c r="R49" s="29" t="n">
+      <x:c r="Q49" s="178"/>
+      <x:c r="R49" s="131" t="n">
         <x:f>IF(Q49="",P49,MAX(P49,Q49))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S49" s="31" t="n">
+      <x:c r="S49" s="168" t="n">
         <x:f>IF(ISNUMBER(H49),R49*H49,"")</x:f>
         <x:v>57.06</x:v>
       </x:c>
-      <x:c r="T49" s="26" t="str">
+      <x:c r="T49" s="142" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U49" s="27" t="str">
+      <x:c r="U49" s="142" t="str">
         <x:v>Full reel preferred. Small orders: Digi-Reel with tape and cover-tape extenders.</x:v>
       </x:c>
-      <x:c r="W49" s="27" t="str">
+      <x:c r="V49" s="142"/>
+      <x:c r="W49" s="142" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X49" s="38" t="d">
+      <x:c r="X49" s="145" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y49" s="27" t="str">
+      <x:c r="Y49" s="142" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="27" hidden="0" customHeight="1">
-      <x:c r="A50" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="B50" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C50" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D50" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="E50" s="16" t="s">
+    <x:row r="50" ht="28" hidden="0" customHeight="1">
+      <x:c r="A50" s="179" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B50" s="179" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C50" s="179" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D50" s="179" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E50" s="169" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F50" s="17" t="n">
+      <x:c r="F50" s="170" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G50" s="17" t="n">
+      <x:c r="G50" s="170" t="n">
         <x:f aca="0">F50*$B$4</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H50" s="18" t="n">
+      <x:c r="H50" s="171" t="n">
         <x:f aca="0">IF(R50&gt;=100,0.2301,IF(R50&gt;=50,0.2494,IF(R50&gt;=10,0.301,IF(R50&gt;=5,0.326,0.39))))</x:f>
         <x:v>0.326</x:v>
       </x:c>
-      <x:c r="I50" s="19" t="n">
+      <x:c r="I50" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H50),F50*H50,"")</x:f>
         <x:v>0.326</x:v>
       </x:c>
-      <x:c r="J50" s="19" t="n">
+      <x:c r="J50" s="172" t="n">
         <x:f aca="0">IF(ISNUMBER(H50),G50*H50,"")</x:f>
         <x:v>1.6300000000000001</x:v>
       </x:c>
-      <x:c r="K50" s="20" t="s">
+      <x:c r="K50" s="169" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L50" s="16" t="s">
+      <x:c r="L50" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M50" s="16" t="str">
+      <x:c r="M50" s="179" t="str">
         <x:f aca="0">IF(ISNUMBER(N50),IF(N50&lt;R50,"Short stock","Available"),"Stock unconfirmed")</x:f>
         <x:v>Available</x:v>
       </x:c>
-      <x:c r="N50" s="40" t="n">
+      <x:c r="N50" s="170" t="n">
         <x:v>42496</x:v>
       </x:c>
-      <x:c r="P50" s="29" t="n">
+      <x:c r="O50" s="167"/>
+      <x:c r="P50" s="170" t="n">
         <x:f>ROUNDUP(G50*1.2,0)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q50" s="30"/>
-      <x:c r="R50" s="29" t="n">
+      <x:c r="Q50" s="178"/>
+      <x:c r="R50" s="170" t="n">
         <x:f>IF(Q50="",P50,MAX(P50,Q50))</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S50" s="31" t="n">
+      <x:c r="S50" s="177" t="n">
         <x:f>IF(ISNUMBER(H50),R50*H50,"")</x:f>
         <x:v>1.956</x:v>
       </x:c>
-      <x:c r="T50" s="26" t="str">
+      <x:c r="T50" s="175" t="str">
         <x:v>Other: +20%</x:v>
       </x:c>
-      <x:c r="U50" s="27" t="str">
+      <x:c r="U50" s="175" t="str">
         <x:v>Confirm packaging and manual assembly with the team.</x:v>
       </x:c>
-      <x:c r="W50" s="27" t="str">
+      <x:c r="V50" s="142"/>
+      <x:c r="W50" s="175" t="str">
         <x:v>Repaired; page verified</x:v>
       </x:c>
-      <x:c r="X50" s="38" t="d">
+      <x:c r="X50" s="176" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="Y50" s="27" t="str">
+      <x:c r="Y50" s="175" t="str">
         <x:v>Exact MPN matched; reported stock. Confirm at checkout.</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="27" hidden="0" customHeight="1">
-      <x:c r="A51" s="1"/>
-      <x:c r="B51" s="1"/>
-      <x:c r="C51" s="1"/>
-      <x:c r="D51" s="1"/>
-      <x:c r="E51" s="1"/>
-      <x:c r="F51" s="1"/>
-      <x:c r="G51" s="1"/>
-      <x:c r="H51" s="1"/>
-      <x:c r="I51" s="1"/>
-      <x:c r="J51" s="1"/>
-      <x:c r="K51" s="1"/>
-      <x:c r="L51" s="1"/>
-      <x:c r="M51" s="1"/>
-      <x:c r="N51" s="1"/>
-      <x:c r="S51" s="32"/>
-    </x:row>
-    <x:row r="52" ht="27" hidden="0" customHeight="1">
-      <x:c r="A52" s="21" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="B52" s="21"/>
-      <x:c r="C52" s="21"/>
-      <x:c r="D52" s="21"/>
-      <x:c r="E52" s="21"/>
-      <x:c r="F52" s="21"/>
-      <x:c r="G52" s="21"/>
-      <x:c r="H52" s="21"/>
-      <x:c r="I52" s="22" t="n">
+    <x:row r="51" ht="22" hidden="0" customHeight="1">
+      <x:c r="A51" s="122"/>
+      <x:c r="B51" s="122"/>
+      <x:c r="C51" s="122"/>
+      <x:c r="D51" s="122"/>
+      <x:c r="E51" s="122"/>
+      <x:c r="F51" s="122"/>
+      <x:c r="G51" s="122"/>
+      <x:c r="H51" s="122"/>
+      <x:c r="I51" s="122"/>
+      <x:c r="J51" s="122"/>
+      <x:c r="K51" s="122"/>
+      <x:c r="L51" s="122"/>
+      <x:c r="M51" s="122"/>
+      <x:c r="N51" s="122"/>
+      <x:c r="O51" s="142"/>
+      <x:c r="P51" s="142"/>
+      <x:c r="Q51" s="142"/>
+      <x:c r="R51" s="142"/>
+      <x:c r="S51" s="144"/>
+      <x:c r="T51" s="142"/>
+      <x:c r="U51" s="142"/>
+      <x:c r="V51" s="142"/>
+      <x:c r="W51" s="142"/>
+      <x:c r="X51" s="142"/>
+      <x:c r="Y51" s="142"/>
+    </x:row>
+    <x:row r="52" ht="25" hidden="0" customHeight="1">
+      <x:c r="A52" s="187" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B52" s="187"/>
+      <x:c r="C52" s="187"/>
+      <x:c r="D52" s="187"/>
+      <x:c r="E52" s="187"/>
+      <x:c r="F52" s="187"/>
+      <x:c r="G52" s="187"/>
+      <x:c r="H52" s="187"/>
+      <x:c r="I52" s="188" t="n">
         <x:f aca="0">SUM(I9:I50)</x:f>
-        <x:v>52.25699999999999</x:v>
-      </x:c>
-      <x:c r="J52" s="22" t="n">
+        <x:v>51.9389</x:v>
+      </x:c>
+      <x:c r="J52" s="188" t="n">
         <x:f aca="0">SUM(J9:J50)</x:f>
-        <x:v>261.28499999999997</x:v>
-      </x:c>
-      <x:c r="K52" s="21"/>
-      <x:c r="L52" s="21"/>
-      <x:c r="M52" s="21"/>
-      <x:c r="N52" s="21"/>
-      <x:c r="P52" s="33" t="str">
+        <x:v>259.6945</x:v>
+      </x:c>
+      <x:c r="K52" s="187"/>
+      <x:c r="L52" s="187"/>
+      <x:c r="M52" s="187"/>
+      <x:c r="N52" s="187"/>
+      <x:c r="O52" s="142"/>
+      <x:c r="P52" s="164" t="str">
         <x:v>PURCHASE TOTAL (USD)</x:v>
       </x:c>
-      <x:c r="Q52" s="33"/>
-      <x:c r="R52" s="33"/>
-      <x:c r="S52" s="34" t="n">
+      <x:c r="Q52" s="164"/>
+      <x:c r="R52" s="164"/>
+      <x:c r="S52" s="190" t="n">
         <x:f>SUM(S9:S50)</x:f>
-        <x:v>705.1752</x:v>
-      </x:c>
+        <x:v>682.8552000000001</x:v>
+      </x:c>
+      <x:c r="T52" s="164"/>
+      <x:c r="U52" s="164"/>
+      <x:c r="V52" s="142"/>
+      <x:c r="W52" s="142"/>
+      <x:c r="X52" s="142"/>
+      <x:c r="Y52" s="142"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="142"/>
+      <x:c r="B53" s="142"/>
+      <x:c r="C53" s="142"/>
+      <x:c r="D53" s="142"/>
+      <x:c r="E53" s="142"/>
+      <x:c r="F53" s="142"/>
+      <x:c r="G53" s="142"/>
+      <x:c r="H53" s="142"/>
+      <x:c r="I53" s="142"/>
+      <x:c r="J53" s="142"/>
+      <x:c r="K53" s="142"/>
+      <x:c r="L53" s="142"/>
+      <x:c r="M53" s="142"/>
+      <x:c r="N53" s="142"/>
+      <x:c r="O53" s="142"/>
+      <x:c r="P53" s="142"/>
+      <x:c r="Q53" s="142"/>
+      <x:c r="R53" s="142"/>
+      <x:c r="S53" s="142"/>
+      <x:c r="T53" s="142"/>
+      <x:c r="U53" s="142"/>
+      <x:c r="V53" s="142"/>
+      <x:c r="W53" s="142"/>
+      <x:c r="X53" s="142"/>
+      <x:c r="Y53" s="142"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="142"/>
+      <x:c r="B54" s="142"/>
+      <x:c r="C54" s="142"/>
+      <x:c r="D54" s="142"/>
+      <x:c r="E54" s="142"/>
+      <x:c r="F54" s="142"/>
+      <x:c r="G54" s="142"/>
+      <x:c r="H54" s="142"/>
+      <x:c r="I54" s="142"/>
+      <x:c r="J54" s="142"/>
+      <x:c r="K54" s="142"/>
+      <x:c r="L54" s="142"/>
+      <x:c r="M54" s="142"/>
+      <x:c r="N54" s="142"/>
+      <x:c r="O54" s="142"/>
+      <x:c r="P54" s="142"/>
+      <x:c r="Q54" s="142"/>
+      <x:c r="R54" s="142"/>
+      <x:c r="S54" s="142"/>
+      <x:c r="T54" s="142"/>
+      <x:c r="U54" s="142"/>
+      <x:c r="V54" s="142"/>
+      <x:c r="W54" s="142"/>
+      <x:c r="X54" s="142"/>
+      <x:c r="Y54" s="142"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="142"/>
+      <x:c r="B55" s="142"/>
+      <x:c r="C55" s="142"/>
+      <x:c r="D55" s="142"/>
+      <x:c r="E55" s="142"/>
+      <x:c r="F55" s="142"/>
+      <x:c r="G55" s="142"/>
+      <x:c r="H55" s="142"/>
+      <x:c r="I55" s="142"/>
+      <x:c r="J55" s="142"/>
+      <x:c r="K55" s="142"/>
+      <x:c r="L55" s="142"/>
+      <x:c r="M55" s="142"/>
+      <x:c r="N55" s="142"/>
+      <x:c r="O55" s="142"/>
+      <x:c r="P55" s="142"/>
+      <x:c r="Q55" s="142"/>
+      <x:c r="R55" s="142"/>
+      <x:c r="S55" s="142"/>
+      <x:c r="T55" s="142"/>
+      <x:c r="U55" s="142"/>
+      <x:c r="V55" s="142"/>
+      <x:c r="W55" s="142"/>
+      <x:c r="X55" s="142"/>
+      <x:c r="Y55" s="142"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5244,13 +5784,8 @@
     <x:mergeCell ref="P6:U6"/>
     <x:mergeCell ref="P7:U7"/>
     <x:mergeCell ref="P52:R52"/>
+    <x:mergeCell ref="A1:N1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="M9:M50">
-    <x:cfRule type="expression" dxfId="0" priority="2" aboveAverage="0" percent="0" bottom="0" rank="0" equalAverage="0">
-      <x:formula>NOT(ISERROR(SEARCH("Short stock",A1)))</x:formula>
-    </x:cfRule>
-    <x:cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Stock unconfirmed"/>
-  </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="whole" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4">
       <x:formula1>1</x:formula1>
@@ -5258,51 +5793,51 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Rea13c52f8c124604"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Radc5d017c8ef45a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R316017bd95194e9d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R26767bccf2b44759"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rd00d99eb7a674473"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R750c6d932c814ef9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Re57bc7b2b59b4787"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rbf3d0f4528184afd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="R0a003a27f8094495"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="R6d29897940904601"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rc43cc238730d4c68"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R1f23888e9d2141f3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R623b9a7c451348f7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R67047e9f99ea4d2f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rf163647432c34955"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="Rc337971a95004862"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R5a855218d5b94c2a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R16345da44de9492d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="Rcde94be920144bfb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R539315d2cf2f4d49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="Ra642c01647f1470c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="Rd4389448a5bf450d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R623098fd1cff4e99"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="R7e3ca50b0cc64d40"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="R0ce85b6cc5f84257"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R2a66da154b50400e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R420a3b914b7c4090"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R79e9e0a81a054c69"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="R0327d90ffd3c4673"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="Rd0d895c6f9dc4ae5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="R7788f510bcbd4308"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R22cbbfb1a8f04ada"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="R24bfe69136314580"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="Rb4b91b2d8ce34a67"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="Ra227599605c244da"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="Rc0e9af25195241cb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="R539435faa2ef4d7b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="Rb9dacf91c5734c87"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="Rf5bec8c878d84090"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="Rcc3d296aceb54aa0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="R56725b5da46b4b27"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="Re8752e39640d463a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R76c4eb5c5ff6483e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R81979a57a56c4884"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R7e2ccdccf1b04ed2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R124642d0a3844da9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rd76556594ac543e7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rdd1a68474f474067"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Rebd6e0e98dbd4336"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R90abf4e9b9d443e1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="R64bb215ab5f94940"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="Rd86c4478d2b941a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R56817c8901ba4b39"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R01ad1f6e7ad546aa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R953be8ac5da94529"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rf32481e53d8f4ca0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R33ad3461a7954a41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R0766df2c35fe47f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R4eb9216660b749b1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R555a4e7a4fff4c62"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="Rea557b12c3674683"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Rd079165abea74dac"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="R24349fda03f047be"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="Rd6d45ddf1ab143d2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R66380de57ee74659"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="R97d538dbdddb4008"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="R58ac4f9d333846f2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R0d637c0eb98440f2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R27287c34c35d4645"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R8f230643f06148d4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="Rac66d31d7e264373"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R018e89adbd264be7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="R49d72d5ca84244be"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R8a7259bc87a845c1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="Rdb0804e759f645de"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="Rf5f129ac3f924b42"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="Rb4c32a9925614e2c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="R1e94658e592c42d9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="Ra5711c258e4f4a3e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="Rb7ceaf5371f44e18"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="R0f50258c88504357"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="Rba4191f514ab48dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="R786c49a32a2e4f49"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="R66908313314a4fb0"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e6572da3f844c05"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d202213244f44f1"/>
 </x:worksheet>
 </file>
 

--- a/engineering/Osiris_PDB_REV1.1_XT60_Procurement_PnP.xlsx
+++ b/engineering/Osiris_PDB_REV1.1_XT60_Procurement_PnP.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement" sheetId="1" r:id="R9e21bc6bba3c4cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="2" r:id="R84b1294069aa4d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement" sheetId="1" r:id="R06626cba86694761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="2" r:id="Rf46dc1ceec2b436f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2069,7 +2069,7 @@
       <x:c r="N2" s="147"/>
       <x:c r="O2" s="142"/>
       <x:c r="P2" s="182" t="str">
-        <x:v>PnP purchasing guidance — October 7, 2026</x:v>
+        <x:v>PnP extra parts and purchasing guidance</x:v>
       </x:c>
       <x:c r="Q2" s="182"/>
       <x:c r="R2" s="182"/>
@@ -2081,7 +2081,7 @@
       <x:c r="X2" s="142"/>
       <x:c r="Y2" s="142"/>
     </x:row>
-    <x:row r="3" ht="23" hidden="0" customHeight="1">
+    <x:row r="3" ht="36" hidden="0" customHeight="1">
       <x:c r="A3" s="124"/>
       <x:c r="B3" s="124"/>
       <x:c r="C3" s="124"/>
@@ -2098,7 +2098,7 @@
       <x:c r="N3" s="124"/>
       <x:c r="O3" s="142"/>
       <x:c r="P3" s="182" t="str">
-        <x:v>Passives: MAX(100, 10 × required qty). All other parts: +20%, rounded up.</x:v>
+        <x:v>Passives: buy at least 100 pieces or 10 times required quantity, whichever is greater. Other parts: 20% extra, rounded up.</x:v>
       </x:c>
       <x:c r="Q3" s="182"/>
       <x:c r="R3" s="182"/>
@@ -2110,7 +2110,7 @@
       <x:c r="X3" s="142"/>
       <x:c r="Y3" s="142"/>
     </x:row>
-    <x:row r="4" ht="23" hidden="0" customHeight="1">
+    <x:row r="4" ht="36" hidden="0" customHeight="1">
       <x:c r="A4" s="152" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -2151,7 +2151,7 @@
       </x:c>
       <x:c r="O4" s="142"/>
       <x:c r="P4" s="182" t="str">
-        <x:v>Full reels preferred. Use Digi-Reel/equivalent extenders for small tape orders.</x:v>
+        <x:v>Buy the Final order qty in column R. Full reels preferred; ask for tape and cover-tape leaders/extenders for small tape orders.</x:v>
       </x:c>
       <x:c r="Q4" s="182"/>
       <x:c r="R4" s="182"/>
@@ -2163,7 +2163,7 @@
       <x:c r="X4" s="142"/>
       <x:c r="Y4" s="142"/>
     </x:row>
-    <x:row r="5" ht="23" hidden="0" customHeight="1">
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
       <x:c r="A5" s="122"/>
       <x:c r="B5" s="122"/>
       <x:c r="C5" s="122"/>
@@ -2180,7 +2180,7 @@
       <x:c r="N5" s="122"/>
       <x:c r="O5" s="142"/>
       <x:c r="P5" s="182" t="str">
-        <x:v>Yellow override: round up for reel/MOQ. Recheck stock and prices at checkout.</x:v>
+        <x:v>Column Q accepts a larger order quantity for reels/MOQ. LCSC substitutions round up to supplier multiples. Recheck stock and prices.</x:v>
       </x:c>
       <x:c r="Q5" s="182"/>
       <x:c r="R5" s="182"/>
@@ -2472,7 +2472,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U10" s="175" t="str">
-        <x:v>Same value/package. 50 V, X7R, ±10%. C91185. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 50 V, X7R, ±10%. C91185. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V10" s="142"/>
       <x:c r="W10" s="175" t="str">
@@ -3017,7 +3017,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U17" s="142" t="str">
-        <x:v>Same value/package. 50 V, X7R, ±10%. C49678. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 50 V, X7R, ±10%. C49678. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V17" s="142"/>
       <x:c r="W17" s="142" t="str">
@@ -4032,7 +4032,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U30" s="175" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C26112. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C26112. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V30" s="142"/>
       <x:c r="W30" s="175" t="str">
@@ -4111,7 +4111,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U31" s="142" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17560. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17560. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V31" s="142"/>
       <x:c r="W31" s="142" t="str">
@@ -4269,7 +4269,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U33" s="142" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17797. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17797. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V33" s="142"/>
       <x:c r="W33" s="142" t="str">
@@ -4348,7 +4348,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U34" s="175" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17539. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17539. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V34" s="142"/>
       <x:c r="W34" s="175" t="str">
@@ -4427,7 +4427,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U35" s="142" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17415. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17415. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V35" s="142"/>
       <x:c r="W35" s="142" t="str">
@@ -4506,7 +4506,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U36" s="175" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17673. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17673. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V36" s="142"/>
       <x:c r="W36" s="175" t="str">
@@ -4664,7 +4664,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U38" s="175" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17513. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17513. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V38" s="142"/>
       <x:c r="W38" s="175" t="str">
@@ -4901,7 +4901,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U41" s="142" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17414. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17414. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V41" s="142"/>
       <x:c r="W41" s="142" t="str">
@@ -5138,7 +5138,7 @@
         <x:v>Passive: 100 or 10×</x:v>
       </x:c>
       <x:c r="U44" s="175" t="str">
-        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17408. Buy one lot per MPN.</x:v>
+        <x:v>Same value/package. 125 mW, 150 V, ±1%. C17408. Buy one lot per MPN. Full reel preferred; request tape/cover-tape leaders for small orders.</x:v>
       </x:c>
       <x:c r="V44" s="142"/>
       <x:c r="W44" s="175" t="str">
@@ -5793,51 +5793,51 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R76c4eb5c5ff6483e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R81979a57a56c4884"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R7e2ccdccf1b04ed2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R124642d0a3844da9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rd76556594ac543e7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rdd1a68474f474067"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Rebd6e0e98dbd4336"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R90abf4e9b9d443e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="R64bb215ab5f94940"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="Rd86c4478d2b941a3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R56817c8901ba4b39"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R01ad1f6e7ad546aa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R953be8ac5da94529"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rf32481e53d8f4ca0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R33ad3461a7954a41"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R0766df2c35fe47f8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R4eb9216660b749b1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R555a4e7a4fff4c62"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="Rea557b12c3674683"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Rd079165abea74dac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="R24349fda03f047be"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="Rd6d45ddf1ab143d2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R66380de57ee74659"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="R97d538dbdddb4008"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="R58ac4f9d333846f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R0d637c0eb98440f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R27287c34c35d4645"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R8f230643f06148d4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="Rac66d31d7e264373"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R018e89adbd264be7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="R49d72d5ca84244be"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R8a7259bc87a845c1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="Rdb0804e759f645de"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="Rf5f129ac3f924b42"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="Rb4c32a9925614e2c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="R1e94658e592c42d9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="Ra5711c258e4f4a3e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="Rb7ceaf5371f44e18"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="R0f50258c88504357"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="Rba4191f514ab48dc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="R786c49a32a2e4f49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="R66908313314a4fb0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R425273b541f94699"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rc5b540feafae47cf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R31df980a8fa34967"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R4030aa2b09be416d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R577393089da548df"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R9b6a23326a334715"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R23c0311105ad4544"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R2f12976fcb2c4ed7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="Re0f35bed6ece4653"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="R5ac792d241f742cc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R95d9052cf16a484a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Ree913fd1c0164949"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R770340699c274cd8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rf28e47914a714807"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R8776175fd86e41a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="Reada309ff92f41ff"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R29441d9e301a449f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R27fe07c573d5415b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R3d0021d1f0084a9c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Ra074ce5555e54b04"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="R4fca9ac153c64416"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="Rfb5dc83b01d544dd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R1f558779162d4473"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="Rac36460eda9b445b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="R869f7b4bc9584c94"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R2a92235a761e41e5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="Rb3a874beef32418e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Re42610016fd84b65"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="Ra8cae8b1acc44c3d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R78a4b473aae64110"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="Rfa2583ac44ff4768"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R4aa663d25242440b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="Rad9277ceda5f4df5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="Rf1a4804b8795489b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="Rfa66edb015d946c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="R190f97f3c5284130"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="Ra2ec0e497b184f4b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="Re9f6faf1712e4d18"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="Rf2ce35d8168441ee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="R277d598a932c4869"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="Rbf331e4579e84c5e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="Rad202e25e27a4220"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d202213244f44f1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb81a28acca44606"/>
 </x:worksheet>
 </file>
 
